--- a/transport/input_data/global/aggregated_transport_data.xlsx
+++ b/transport/input_data/global/aggregated_transport_data.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="888" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="948" uniqueCount="57">
   <si>
     <t>Country</t>
   </si>
@@ -52,6 +52,9 @@
     <t>Colombia</t>
   </si>
   <si>
+    <t>Democratic Republic of the Congo</t>
+  </si>
+  <si>
     <t>Egypt</t>
   </si>
   <si>
@@ -76,6 +79,9 @@
     <t>Italy</t>
   </si>
   <si>
+    <t>Italy-San Marino</t>
+  </si>
+  <si>
     <t>Japan</t>
   </si>
   <si>
@@ -94,6 +100,9 @@
     <t>Namibia</t>
   </si>
   <si>
+    <t>Niger</t>
+  </si>
+  <si>
     <t>Nigeria</t>
   </si>
   <si>
@@ -104,6 +113,9 @@
   </si>
   <si>
     <t>Russia</t>
+  </si>
+  <si>
+    <t>Russian Federation</t>
   </si>
   <si>
     <t>Saudi Arabia</t>
@@ -124,10 +136,16 @@
     <t>United Kingdom</t>
   </si>
   <si>
+    <t>United Republic of Tanzania</t>
+  </si>
+  <si>
     <t>United States of America</t>
   </si>
   <si>
     <t>Venezuela</t>
+  </si>
+  <si>
+    <t>Venezuela (Bolivarian Republic of)</t>
   </si>
   <si>
     <t>2011</t>
@@ -524,7 +542,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D443"/>
+  <dimension ref="A1:D473"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -546,7 +564,7 @@
         <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="C2">
         <v>5.561388888888889</v>
@@ -560,7 +578,7 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="C3">
         <v>6.198611111111111</v>
@@ -574,7 +592,7 @@
         <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="C4">
         <v>6.406666666666666</v>
@@ -588,7 +606,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="C5">
         <v>5.083611111111111</v>
@@ -602,7 +620,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="C6">
         <v>5.561388888888889</v>
@@ -616,7 +634,7 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="C7">
         <v>4.618333333333333</v>
@@ -630,7 +648,7 @@
         <v>4</v>
       </c>
       <c r="B8" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="C8">
         <v>4.348611111111111</v>
@@ -644,7 +662,7 @@
         <v>4</v>
       </c>
       <c r="B9" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="C9">
         <v>5.316388888888889</v>
@@ -658,7 +676,7 @@
         <v>4</v>
       </c>
       <c r="B10" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="C10">
         <v>4.336388888888889</v>
@@ -672,7 +690,7 @@
         <v>4</v>
       </c>
       <c r="B11" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="C11">
         <v>2.658333333333333</v>
@@ -686,7 +704,7 @@
         <v>4</v>
       </c>
       <c r="B12" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="C12">
         <v>2.731666666666666</v>
@@ -700,7 +718,7 @@
         <v>4</v>
       </c>
       <c r="B13" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="C13">
         <v>4.266944444444444</v>
@@ -714,7 +732,7 @@
         <v>4</v>
       </c>
       <c r="B14" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="C14">
         <v>6.777222222222222</v>
@@ -728,7 +746,7 @@
         <v>5</v>
       </c>
       <c r="B15" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="C15">
         <v>8.501388888888888</v>
@@ -742,7 +760,7 @@
         <v>5</v>
       </c>
       <c r="B16" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="C16">
         <v>8.489166666666666</v>
@@ -756,7 +774,7 @@
         <v>5</v>
       </c>
       <c r="B17" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="C17">
         <v>10.89027777777778</v>
@@ -770,7 +788,7 @@
         <v>5</v>
       </c>
       <c r="B18" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="C18">
         <v>10.79222222222222</v>
@@ -784,7 +802,7 @@
         <v>5</v>
       </c>
       <c r="B19" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="C19">
         <v>10.97611111111111</v>
@@ -798,7 +816,7 @@
         <v>5</v>
       </c>
       <c r="B20" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="C20">
         <v>11.33111111111111</v>
@@ -812,7 +830,7 @@
         <v>5</v>
       </c>
       <c r="B21" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="C21">
         <v>12.02944444444444</v>
@@ -826,7 +844,7 @@
         <v>5</v>
       </c>
       <c r="B22" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="C22">
         <v>10.93916666666667</v>
@@ -840,7 +858,7 @@
         <v>5</v>
       </c>
       <c r="B23" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="C23">
         <v>10.80444444444444</v>
@@ -854,7 +872,7 @@
         <v>5</v>
       </c>
       <c r="B24" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="C24">
         <v>4.613333333333333</v>
@@ -868,7 +886,7 @@
         <v>5</v>
       </c>
       <c r="B25" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="C25">
         <v>4.65</v>
@@ -882,7 +900,7 @@
         <v>5</v>
       </c>
       <c r="B26" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="C26">
         <v>9.015277777777778</v>
@@ -896,7 +914,7 @@
         <v>5</v>
       </c>
       <c r="B27" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="C27">
         <v>11.62527777777778</v>
@@ -910,7 +928,7 @@
         <v>6</v>
       </c>
       <c r="B28" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="C28">
         <v>38.28111111111111</v>
@@ -924,7 +942,7 @@
         <v>6</v>
       </c>
       <c r="B29" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="C29">
         <v>39.72666666666667</v>
@@ -938,7 +956,7 @@
         <v>6</v>
       </c>
       <c r="B30" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="C30">
         <v>41.82138888888889</v>
@@ -952,7 +970,7 @@
         <v>6</v>
       </c>
       <c r="B31" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="C31">
         <v>45.11666666666667</v>
@@ -966,7 +984,7 @@
         <v>6</v>
       </c>
       <c r="B32" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="C32">
         <v>44.835</v>
@@ -980,7 +998,7 @@
         <v>6</v>
       </c>
       <c r="B33" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="C33">
         <v>47.8975</v>
@@ -994,7 +1012,7 @@
         <v>6</v>
       </c>
       <c r="B34" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="C34">
         <v>51.63</v>
@@ -1008,7 +1026,7 @@
         <v>6</v>
       </c>
       <c r="B35" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="C35">
         <v>54.68305555555555</v>
@@ -1022,7 +1040,7 @@
         <v>6</v>
       </c>
       <c r="B36" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="C36">
         <v>58.1825</v>
@@ -1036,7 +1054,7 @@
         <v>6</v>
       </c>
       <c r="B37" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="C37">
         <v>44.60027777777778</v>
@@ -1050,7 +1068,7 @@
         <v>6</v>
       </c>
       <c r="B38" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="C38">
         <v>14.56805555555556</v>
@@ -1064,7 +1082,7 @@
         <v>6</v>
       </c>
       <c r="B39" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="C39">
         <v>20.40527777777778</v>
@@ -1078,7 +1096,7 @@
         <v>6</v>
       </c>
       <c r="B40" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="C40">
         <v>36.60055555555556</v>
@@ -1092,7 +1110,7 @@
         <v>7</v>
       </c>
       <c r="B41" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="C41">
         <v>25.16138888888889</v>
@@ -1106,7 +1124,7 @@
         <v>7</v>
       </c>
       <c r="B42" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="C42">
         <v>26.15361111111111</v>
@@ -1120,7 +1138,7 @@
         <v>7</v>
       </c>
       <c r="B43" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="C43">
         <v>27.29305555555555</v>
@@ -1134,7 +1152,7 @@
         <v>7</v>
       </c>
       <c r="B44" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="C44">
         <v>29.16722222222222</v>
@@ -1148,7 +1166,7 @@
         <v>7</v>
       </c>
       <c r="B45" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="C45">
         <v>28.48111111111111</v>
@@ -1162,7 +1180,7 @@
         <v>7</v>
       </c>
       <c r="B46" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="C46">
         <v>26.43555555555556</v>
@@ -1176,7 +1194,7 @@
         <v>7</v>
       </c>
       <c r="B47" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="C47">
         <v>25.8475</v>
@@ -1190,7 +1208,7 @@
         <v>7</v>
       </c>
       <c r="B48" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="C48">
         <v>29.30194444444444</v>
@@ -1204,7 +1222,7 @@
         <v>7</v>
       </c>
       <c r="B49" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="C49">
         <v>28.38333333333333</v>
@@ -1218,7 +1236,7 @@
         <v>7</v>
       </c>
       <c r="B50" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="C50">
         <v>11.95611111111111</v>
@@ -1232,7 +1250,7 @@
         <v>7</v>
       </c>
       <c r="B51" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="C51">
         <v>12.82416666666667</v>
@@ -1246,7 +1264,7 @@
         <v>7</v>
       </c>
       <c r="B52" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="C52">
         <v>20.87722222222222</v>
@@ -1260,7 +1278,7 @@
         <v>7</v>
       </c>
       <c r="B53" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="C53">
         <v>24.48527777777778</v>
@@ -1274,7 +1292,7 @@
         <v>8</v>
       </c>
       <c r="B54" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="C54">
         <v>35.95388888888889</v>
@@ -1288,7 +1306,7 @@
         <v>8</v>
       </c>
       <c r="B55" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="C55">
         <v>40.59666666666666</v>
@@ -1302,7 +1320,7 @@
         <v>8</v>
       </c>
       <c r="B56" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="C56">
         <v>42.37277777777778</v>
@@ -1316,7 +1334,7 @@
         <v>8</v>
       </c>
       <c r="B57" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="C57">
         <v>42.0175</v>
@@ -1330,7 +1348,7 @@
         <v>8</v>
       </c>
       <c r="B58" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="C58">
         <v>43.49972222222222</v>
@@ -1344,7 +1362,7 @@
         <v>8</v>
       </c>
       <c r="B59" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="C59">
         <v>45.76611111111111</v>
@@ -1358,7 +1376,7 @@
         <v>8</v>
       </c>
       <c r="B60" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="C60">
         <v>50.08888888888889</v>
@@ -1372,7 +1390,7 @@
         <v>8</v>
       </c>
       <c r="B61" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="C61">
         <v>57.17388888888889</v>
@@ -1386,7 +1404,7 @@
         <v>8</v>
       </c>
       <c r="B62" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="C62">
         <v>57.77027777777778</v>
@@ -1400,7 +1418,7 @@
         <v>8</v>
       </c>
       <c r="B63" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="C63">
         <v>25.07194444444444</v>
@@ -1414,7 +1432,7 @@
         <v>8</v>
       </c>
       <c r="B64" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="C64">
         <v>25.18222222222222</v>
@@ -1428,7 +1446,7 @@
         <v>8</v>
       </c>
       <c r="B65" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="C65">
         <v>43.41583333333333</v>
@@ -1442,7 +1460,7 @@
         <v>8</v>
       </c>
       <c r="B66" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="C66">
         <v>51.6675</v>
@@ -1456,7 +1474,7 @@
         <v>9</v>
       </c>
       <c r="B67" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="C67">
         <v>5.083611111111111</v>
@@ -1470,7 +1488,7 @@
         <v>9</v>
       </c>
       <c r="B68" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="C68">
         <v>8.183055555555555</v>
@@ -1484,7 +1502,7 @@
         <v>9</v>
       </c>
       <c r="B69" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="C69">
         <v>7.239722222222222</v>
@@ -1498,7 +1516,7 @@
         <v>9</v>
       </c>
       <c r="B70" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="C70">
         <v>7.533611111111111</v>
@@ -1512,7 +1530,7 @@
         <v>9</v>
       </c>
       <c r="B71" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="C71">
         <v>6.516944444444444</v>
@@ -1526,7 +1544,7 @@
         <v>9</v>
       </c>
       <c r="B72" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="C72">
         <v>6.713055555555556</v>
@@ -1540,7 +1558,7 @@
         <v>9</v>
       </c>
       <c r="B73" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="C73">
         <v>7.091944444444445</v>
@@ -1554,7 +1572,7 @@
         <v>9</v>
       </c>
       <c r="B74" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="C74">
         <v>7.791388888888889</v>
@@ -1568,7 +1586,7 @@
         <v>9</v>
       </c>
       <c r="B75" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="C75">
         <v>8.836666666666666</v>
@@ -1582,7 +1600,7 @@
         <v>9</v>
       </c>
       <c r="B76" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="C76">
         <v>4.733333333333333</v>
@@ -1596,7 +1614,7 @@
         <v>9</v>
       </c>
       <c r="B77" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="C77">
         <v>5.256111111111111</v>
@@ -1610,7 +1628,7 @@
         <v>9</v>
       </c>
       <c r="B78" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="C78">
         <v>7.254166666666666</v>
@@ -1624,7 +1642,7 @@
         <v>9</v>
       </c>
       <c r="B79" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="C79">
         <v>8.060833333333333</v>
@@ -1638,7 +1656,7 @@
         <v>10</v>
       </c>
       <c r="B80" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="C80">
         <v>69.01666666666667</v>
@@ -1652,7 +1670,7 @@
         <v>10</v>
       </c>
       <c r="B81" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="C81">
         <v>72.67277777777778</v>
@@ -1666,7 +1684,7 @@
         <v>10</v>
       </c>
       <c r="B82" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="C82">
         <v>77.78277777777778</v>
@@ -1680,7 +1698,7 @@
         <v>10</v>
       </c>
       <c r="B83" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="C83">
         <v>85.28333333333333</v>
@@ -1694,7 +1712,7 @@
         <v>10</v>
       </c>
       <c r="B84" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="C84">
         <v>92.75944444444444</v>
@@ -1708,7 +1726,7 @@
         <v>10</v>
       </c>
       <c r="B85" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="C85">
         <v>102.4466666666667</v>
@@ -1722,7 +1740,7 @@
         <v>10</v>
       </c>
       <c r="B86" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="C86">
         <v>113.7425</v>
@@ -1736,7 +1754,7 @@
         <v>10</v>
       </c>
       <c r="B87" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="C87">
         <v>123.6858333333333</v>
@@ -1750,7 +1768,7 @@
         <v>10</v>
       </c>
       <c r="B88" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="C88">
         <v>127.5972222222222</v>
@@ -1764,7 +1782,7 @@
         <v>10</v>
       </c>
       <c r="B89" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="C89">
         <v>58.44472222222223</v>
@@ -1778,7 +1796,7 @@
         <v>10</v>
       </c>
       <c r="B90" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="C90">
         <v>53.64277777777778</v>
@@ -1792,7 +1810,7 @@
         <v>10</v>
       </c>
       <c r="B91" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="C91">
         <v>47.18444444444444</v>
@@ -1806,7 +1824,7 @@
         <v>10</v>
       </c>
       <c r="B92" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="C92">
         <v>73.82083333333334</v>
@@ -1820,7 +1838,7 @@
         <v>11</v>
       </c>
       <c r="B93" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="C93">
         <v>5.524722222222223</v>
@@ -1834,7 +1852,7 @@
         <v>11</v>
       </c>
       <c r="B94" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="C94">
         <v>6.051388888888889</v>
@@ -1848,7 +1866,7 @@
         <v>11</v>
       </c>
       <c r="B95" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="C95">
         <v>6.37</v>
@@ -1862,7 +1880,7 @@
         <v>11</v>
       </c>
       <c r="B96" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="C96">
         <v>8.183055555555555</v>
@@ -1876,7 +1894,7 @@
         <v>11</v>
       </c>
       <c r="B97" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="C97">
         <v>8.832222222222223</v>
@@ -1890,7 +1908,7 @@
         <v>11</v>
       </c>
       <c r="B98" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="C98">
         <v>8.86888888888889</v>
@@ -1904,7 +1922,7 @@
         <v>11</v>
       </c>
       <c r="B99" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="C99">
         <v>9.088333333333333</v>
@@ -1918,7 +1936,7 @@
         <v>11</v>
       </c>
       <c r="B100" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="C100">
         <v>10.39055555555556</v>
@@ -1932,7 +1950,7 @@
         <v>11</v>
       </c>
       <c r="B101" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="C101">
         <v>10.5775</v>
@@ -1946,7 +1964,7 @@
         <v>11</v>
       </c>
       <c r="B102" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="C102">
         <v>4.895833333333333</v>
@@ -1960,7 +1978,7 @@
         <v>11</v>
       </c>
       <c r="B103" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="C103">
         <v>5.739166666666667</v>
@@ -1974,7 +1992,7 @@
         <v>11</v>
       </c>
       <c r="B104" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="C104">
         <v>11.20555555555556</v>
@@ -1988,7 +2006,7 @@
         <v>11</v>
       </c>
       <c r="B105" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="C105">
         <v>10.44277777777778</v>
@@ -2002,13 +2020,13 @@
         <v>12</v>
       </c>
       <c r="B106" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="C106">
-        <v>9.444722222222222</v>
+        <v>1.631666666666667</v>
       </c>
       <c r="D106">
-        <v>4.408611111111111</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -2016,13 +2034,13 @@
         <v>12</v>
       </c>
       <c r="B107" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="C107">
-        <v>9.983611111111111</v>
+        <v>1.206666666666667</v>
       </c>
       <c r="D107">
-        <v>4.030833333333334</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -2030,13 +2048,13 @@
         <v>12</v>
       </c>
       <c r="B108" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="C108">
-        <v>6.908888888888889</v>
+        <v>1.477777777777778</v>
       </c>
       <c r="D108">
-        <v>2.820555555555555</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -2044,13 +2062,13 @@
         <v>12</v>
       </c>
       <c r="B109" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="C109">
-        <v>8.146111111111111</v>
+        <v>0.9791666666666666</v>
       </c>
       <c r="D109">
-        <v>1.865277777777778</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -2058,125 +2076,125 @@
         <v>12</v>
       </c>
       <c r="B110" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="C110">
-        <v>6.198611111111111</v>
+        <v>0.6288888888888889</v>
       </c>
       <c r="D110">
-        <v>2.061666666666667</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111" spans="1:4">
       <c r="A111" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B111" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C111">
-        <v>5.206111111111111</v>
+        <v>9.444722222222222</v>
       </c>
       <c r="D111">
-        <v>0.6058333333333333</v>
+        <v>4.408611111111111</v>
       </c>
     </row>
     <row r="112" spans="1:4">
       <c r="A112" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B112" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C112">
-        <v>7.643888888888889</v>
+        <v>9.983611111111111</v>
       </c>
       <c r="D112">
-        <v>1.043611111111111</v>
+        <v>4.030833333333334</v>
       </c>
     </row>
     <row r="113" spans="1:4">
       <c r="A113" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B113" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C113">
-        <v>8.795555555555556</v>
+        <v>6.908888888888889</v>
       </c>
       <c r="D113">
-        <v>5.028055555555556</v>
+        <v>2.820555555555555</v>
       </c>
     </row>
     <row r="114" spans="1:4">
       <c r="A114" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B114" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C114">
-        <v>7.852222222222222</v>
+        <v>8.146111111111111</v>
       </c>
       <c r="D114">
-        <v>4.629166666666666</v>
+        <v>1.865277777777778</v>
       </c>
     </row>
     <row r="115" spans="1:4">
       <c r="A115" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B115" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C115">
-        <v>3.7425</v>
+        <v>6.198611111111111</v>
       </c>
       <c r="D115">
-        <v>4.375833333333333</v>
+        <v>2.061666666666667</v>
       </c>
     </row>
     <row r="116" spans="1:4">
       <c r="A116" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B116" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C116">
-        <v>3.273611111111111</v>
+        <v>5.206111111111111</v>
       </c>
       <c r="D116">
-        <v>4.570833333333334</v>
+        <v>0.6058333333333333</v>
       </c>
     </row>
     <row r="117" spans="1:4">
       <c r="A117" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B117" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C117">
-        <v>3.124444444444444</v>
+        <v>7.643888888888889</v>
       </c>
       <c r="D117">
-        <v>4.174166666666666</v>
+        <v>1.043611111111111</v>
       </c>
     </row>
     <row r="118" spans="1:4">
       <c r="A118" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B118" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C118">
-        <v>12.59305555555556</v>
+        <v>8.795555555555556</v>
       </c>
       <c r="D118">
-        <v>2.120277777777778</v>
+        <v>5.028055555555556</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -2184,13 +2202,13 @@
         <v>13</v>
       </c>
       <c r="B119" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="C119">
-        <v>3.601388888888889</v>
+        <v>7.852222222222222</v>
       </c>
       <c r="D119">
-        <v>0</v>
+        <v>4.629166666666666</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -2198,13 +2216,13 @@
         <v>13</v>
       </c>
       <c r="B120" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="C120">
-        <v>4.311944444444444</v>
+        <v>3.7425</v>
       </c>
       <c r="D120">
-        <v>0</v>
+        <v>4.375833333333333</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -2212,13 +2230,13 @@
         <v>13</v>
       </c>
       <c r="B121" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="C121">
-        <v>4.667222222222223</v>
+        <v>3.273611111111111</v>
       </c>
       <c r="D121">
-        <v>0</v>
+        <v>4.570833333333334</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -2226,13 +2244,13 @@
         <v>13</v>
       </c>
       <c r="B122" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="C122">
-        <v>5.255277777777778</v>
+        <v>3.124444444444444</v>
       </c>
       <c r="D122">
-        <v>0</v>
+        <v>4.174166666666666</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -2240,24 +2258,24 @@
         <v>13</v>
       </c>
       <c r="B123" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="C123">
-        <v>5.573611111111111</v>
+        <v>12.59305555555556</v>
       </c>
       <c r="D123">
-        <v>0</v>
+        <v>2.120277777777778</v>
       </c>
     </row>
     <row r="124" spans="1:4">
       <c r="A124" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B124" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C124">
-        <v>7.203055555555555</v>
+        <v>3.601388888888889</v>
       </c>
       <c r="D124">
         <v>0</v>
@@ -2265,13 +2283,13 @@
     </row>
     <row r="125" spans="1:4">
       <c r="A125" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B125" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C125">
-        <v>8.359166666666667</v>
+        <v>4.311944444444444</v>
       </c>
       <c r="D125">
         <v>0</v>
@@ -2279,13 +2297,13 @@
     </row>
     <row r="126" spans="1:4">
       <c r="A126" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B126" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C126">
-        <v>8.955555555555556</v>
+        <v>4.667222222222223</v>
       </c>
       <c r="D126">
         <v>0</v>
@@ -2293,13 +2311,13 @@
     </row>
     <row r="127" spans="1:4">
       <c r="A127" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B127" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C127">
-        <v>10.045</v>
+        <v>5.255277777777778</v>
       </c>
       <c r="D127">
         <v>0</v>
@@ -2307,13 +2325,13 @@
     </row>
     <row r="128" spans="1:4">
       <c r="A128" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B128" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C128">
-        <v>4.641666666666667</v>
+        <v>5.573611111111111</v>
       </c>
       <c r="D128">
         <v>0</v>
@@ -2321,13 +2339,13 @@
     </row>
     <row r="129" spans="1:4">
       <c r="A129" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B129" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C129">
-        <v>10.10444444444444</v>
+        <v>7.203055555555555</v>
       </c>
       <c r="D129">
         <v>0</v>
@@ -2335,13 +2353,13 @@
     </row>
     <row r="130" spans="1:4">
       <c r="A130" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B130" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C130">
-        <v>11.57111111111111</v>
+        <v>8.359166666666667</v>
       </c>
       <c r="D130">
         <v>0</v>
@@ -2349,13 +2367,13 @@
     </row>
     <row r="131" spans="1:4">
       <c r="A131" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B131" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C131">
-        <v>13.60027777777778</v>
+        <v>8.955555555555556</v>
       </c>
       <c r="D131">
         <v>0</v>
@@ -2366,13 +2384,13 @@
         <v>14</v>
       </c>
       <c r="B132" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="C132">
-        <v>65.75805555555556</v>
+        <v>10.045</v>
       </c>
       <c r="D132">
-        <v>30.93666666666667</v>
+        <v>0</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -2380,13 +2398,13 @@
         <v>14</v>
       </c>
       <c r="B133" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="C133">
-        <v>64.36138888888888</v>
+        <v>4.641666666666667</v>
       </c>
       <c r="D133">
-        <v>29.29444444444444</v>
+        <v>0</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -2394,13 +2412,13 @@
         <v>14</v>
       </c>
       <c r="B134" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="C134">
-        <v>63.79805555555556</v>
+        <v>10.10444444444444</v>
       </c>
       <c r="D134">
-        <v>26.75833333333333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -2408,13 +2426,13 @@
         <v>14</v>
       </c>
       <c r="B135" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="C135">
-        <v>64.41055555555556</v>
+        <v>11.57111111111111</v>
       </c>
       <c r="D135">
-        <v>22.92416666666667</v>
+        <v>0</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -2422,125 +2440,125 @@
         <v>14</v>
       </c>
       <c r="B136" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="C136">
-        <v>68.19583333333334</v>
+        <v>13.60027777777778</v>
       </c>
       <c r="D136">
-        <v>20.52388888888889</v>
+        <v>0</v>
       </c>
     </row>
     <row r="137" spans="1:4">
       <c r="A137" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B137" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C137">
-        <v>67.06861111111111</v>
+        <v>65.75805555555556</v>
       </c>
       <c r="D137">
-        <v>19.48</v>
+        <v>30.93666666666667</v>
       </c>
     </row>
     <row r="138" spans="1:4">
       <c r="A138" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B138" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C138">
-        <v>68.12666666666667</v>
+        <v>64.36138888888888</v>
       </c>
       <c r="D138">
-        <v>20.53916666666667</v>
+        <v>29.29444444444444</v>
       </c>
     </row>
     <row r="139" spans="1:4">
       <c r="A139" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B139" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C139">
-        <v>70.50722222222223</v>
+        <v>63.79805555555556</v>
       </c>
       <c r="D139">
-        <v>23.125</v>
+        <v>26.75833333333333</v>
       </c>
     </row>
     <row r="140" spans="1:4">
       <c r="A140" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B140" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C140">
-        <v>74.05527777777777</v>
+        <v>64.41055555555556</v>
       </c>
       <c r="D140">
-        <v>20.22305555555555</v>
+        <v>22.92416666666667</v>
       </c>
     </row>
     <row r="141" spans="1:4">
       <c r="A141" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B141" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C141">
-        <v>31.44361111111111</v>
+        <v>68.19583333333334</v>
       </c>
       <c r="D141">
-        <v>11.58444444444445</v>
+        <v>20.52388888888889</v>
       </c>
     </row>
     <row r="142" spans="1:4">
       <c r="A142" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B142" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C142">
-        <v>34.19</v>
+        <v>67.06861111111111</v>
       </c>
       <c r="D142">
-        <v>13.15111111111111</v>
+        <v>19.48</v>
       </c>
     </row>
     <row r="143" spans="1:4">
       <c r="A143" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B143" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C143">
-        <v>58.5775</v>
+        <v>68.12666666666667</v>
       </c>
       <c r="D143">
-        <v>13.88111111111111</v>
+        <v>20.53916666666667</v>
       </c>
     </row>
     <row r="144" spans="1:4">
       <c r="A144" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B144" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C144">
-        <v>64.37638888888888</v>
+        <v>70.50722222222223</v>
       </c>
       <c r="D144">
-        <v>12.45138888888889</v>
+        <v>23.125</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -2548,13 +2566,13 @@
         <v>15</v>
       </c>
       <c r="B145" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="C145">
-        <v>91.74027777777778</v>
+        <v>74.05527777777777</v>
       </c>
       <c r="D145">
-        <v>31.67472222222222</v>
+        <v>20.22305555555555</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -2562,13 +2580,13 @@
         <v>15</v>
       </c>
       <c r="B146" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="C146">
-        <v>97.8775</v>
+        <v>31.44361111111111</v>
       </c>
       <c r="D146">
-        <v>29.56888888888889</v>
+        <v>11.58444444444445</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -2576,13 +2594,13 @@
         <v>15</v>
       </c>
       <c r="B147" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="C147">
-        <v>99.83750000000001</v>
+        <v>34.19</v>
       </c>
       <c r="D147">
-        <v>26.73666666666667</v>
+        <v>13.15111111111111</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -2590,13 +2608,13 @@
         <v>15</v>
       </c>
       <c r="B148" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="C148">
-        <v>95.86861111111111</v>
+        <v>58.5775</v>
       </c>
       <c r="D148">
-        <v>26.80472222222222</v>
+        <v>13.88111111111111</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -2604,125 +2622,125 @@
         <v>15</v>
       </c>
       <c r="B149" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="C149">
-        <v>95.99111111111111</v>
+        <v>64.37638888888888</v>
       </c>
       <c r="D149">
-        <v>28.09361111111111</v>
+        <v>12.45138888888889</v>
       </c>
     </row>
     <row r="150" spans="1:4">
       <c r="A150" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B150" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C150">
-        <v>103.2552777777778</v>
+        <v>91.74027777777778</v>
       </c>
       <c r="D150">
-        <v>32.76083333333333</v>
+        <v>31.67472222222222</v>
       </c>
     </row>
     <row r="151" spans="1:4">
       <c r="A151" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B151" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C151">
-        <v>114.1577777777778</v>
+        <v>97.8775</v>
       </c>
       <c r="D151">
-        <v>26.65805555555556</v>
+        <v>29.56888888888889</v>
       </c>
     </row>
     <row r="152" spans="1:4">
       <c r="A152" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B152" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C152">
-        <v>117.7347222222222</v>
+        <v>99.83750000000001</v>
       </c>
       <c r="D152">
-        <v>19.77611111111111</v>
+        <v>26.73666666666667</v>
       </c>
     </row>
     <row r="153" spans="1:4">
       <c r="A153" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B153" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C153">
-        <v>116.7669444444444</v>
+        <v>95.86861111111111</v>
       </c>
       <c r="D153">
-        <v>15.92916666666667</v>
+        <v>26.80472222222222</v>
       </c>
     </row>
     <row r="154" spans="1:4">
       <c r="A154" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B154" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C154">
-        <v>53.99805555555555</v>
+        <v>95.99111111111111</v>
       </c>
       <c r="D154">
-        <v>15.43333333333333</v>
+        <v>28.09361111111111</v>
       </c>
     </row>
     <row r="155" spans="1:4">
       <c r="A155" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B155" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C155">
-        <v>72.11583333333333</v>
+        <v>103.2552777777778</v>
       </c>
       <c r="D155">
-        <v>16.36833333333333</v>
+        <v>32.76083333333333</v>
       </c>
     </row>
     <row r="156" spans="1:4">
       <c r="A156" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B156" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C156">
-        <v>107.1752777777778</v>
+        <v>114.1577777777778</v>
       </c>
       <c r="D156">
-        <v>17.16722222222222</v>
+        <v>26.65805555555556</v>
       </c>
     </row>
     <row r="157" spans="1:4">
       <c r="A157" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B157" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C157">
-        <v>111.7566666666667</v>
+        <v>117.7347222222222</v>
       </c>
       <c r="D157">
-        <v>15.25194444444444</v>
+        <v>19.77611111111111</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -2730,13 +2748,13 @@
         <v>16</v>
       </c>
       <c r="B158" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="C158">
-        <v>1.646666666666667</v>
+        <v>116.7669444444444</v>
       </c>
       <c r="D158">
-        <v>0.9805555555555555</v>
+        <v>15.92916666666667</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -2744,13 +2762,13 @@
         <v>16</v>
       </c>
       <c r="B159" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="C159">
-        <v>1.690833333333333</v>
+        <v>53.99805555555555</v>
       </c>
       <c r="D159">
-        <v>0.965</v>
+        <v>15.43333333333333</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -2758,13 +2776,13 @@
         <v>16</v>
       </c>
       <c r="B160" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="C160">
-        <v>1.596666666666667</v>
+        <v>72.11583333333333</v>
       </c>
       <c r="D160">
-        <v>0.6186111111111111</v>
+        <v>16.36833333333333</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -2772,13 +2790,13 @@
         <v>16</v>
       </c>
       <c r="B161" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="C161">
-        <v>1.391944444444444</v>
+        <v>107.1752777777778</v>
       </c>
       <c r="D161">
-        <v>0.1288888888888889</v>
+        <v>17.16722222222222</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -2786,125 +2804,125 @@
         <v>16</v>
       </c>
       <c r="B162" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="C162">
-        <v>1.223333333333333</v>
+        <v>111.7566666666667</v>
       </c>
       <c r="D162">
-        <v>0.04888888888888889</v>
+        <v>15.25194444444444</v>
       </c>
     </row>
     <row r="163" spans="1:4">
       <c r="A163" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B163" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C163">
-        <v>1.598055555555556</v>
+        <v>1.646666666666667</v>
       </c>
       <c r="D163">
-        <v>0.02861111111111111</v>
+        <v>0.9805555555555555</v>
       </c>
     </row>
     <row r="164" spans="1:4">
       <c r="A164" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B164" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C164">
-        <v>1.749722222222222</v>
+        <v>1.690833333333333</v>
       </c>
       <c r="D164">
-        <v>1.061944444444444</v>
+        <v>0.965</v>
       </c>
     </row>
     <row r="165" spans="1:4">
       <c r="A165" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B165" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C165">
-        <v>2.136388888888889</v>
+        <v>1.596666666666667</v>
       </c>
       <c r="D165">
-        <v>0.1230555555555556</v>
+        <v>0.6186111111111111</v>
       </c>
     </row>
     <row r="166" spans="1:4">
       <c r="A166" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B166" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C166">
-        <v>2.599444444444444</v>
+        <v>1.391944444444444</v>
       </c>
       <c r="D166">
-        <v>0.08611111111111111</v>
+        <v>0.1288888888888889</v>
       </c>
     </row>
     <row r="167" spans="1:4">
       <c r="A167" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B167" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C167">
-        <v>1.476111111111111</v>
+        <v>1.223333333333333</v>
       </c>
       <c r="D167">
-        <v>0.0625</v>
+        <v>0.04888888888888889</v>
       </c>
     </row>
     <row r="168" spans="1:4">
       <c r="A168" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B168" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C168">
-        <v>2.341388888888889</v>
+        <v>1.598055555555556</v>
       </c>
       <c r="D168">
-        <v>0.08222222222222222</v>
+        <v>0.02861111111111111</v>
       </c>
     </row>
     <row r="169" spans="1:4">
       <c r="A169" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B169" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C169">
-        <v>2.345</v>
+        <v>1.749722222222222</v>
       </c>
       <c r="D169">
-        <v>0.02805555555555556</v>
+        <v>1.061944444444444</v>
       </c>
     </row>
     <row r="170" spans="1:4">
       <c r="A170" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B170" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C170">
-        <v>2.386111111111111</v>
+        <v>2.136388888888889</v>
       </c>
       <c r="D170">
-        <v>0.04277777777777778</v>
+        <v>0.1230555555555556</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -2912,13 +2930,13 @@
         <v>17</v>
       </c>
       <c r="B171" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="C171">
-        <v>57.80777777777778</v>
+        <v>2.599444444444444</v>
       </c>
       <c r="D171">
-        <v>0</v>
+        <v>0.08611111111111111</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -2926,13 +2944,13 @@
         <v>17</v>
       </c>
       <c r="B172" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="C172">
-        <v>57.80777777777778</v>
+        <v>1.476111111111111</v>
       </c>
       <c r="D172">
-        <v>0</v>
+        <v>0.0625</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -2940,13 +2958,13 @@
         <v>17</v>
       </c>
       <c r="B173" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="C173">
-        <v>47.19916666666666</v>
+        <v>2.341388888888889</v>
       </c>
       <c r="D173">
-        <v>14.58416666666667</v>
+        <v>0.08222222222222222</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -2954,13 +2972,13 @@
         <v>17</v>
       </c>
       <c r="B174" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="C174">
-        <v>46.52555555555556</v>
+        <v>2.345</v>
       </c>
       <c r="D174">
-        <v>15.15</v>
+        <v>0.02805555555555556</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -2968,125 +2986,125 @@
         <v>17</v>
       </c>
       <c r="B175" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="C175">
-        <v>53.69166666666667</v>
+        <v>2.386111111111111</v>
       </c>
       <c r="D175">
-        <v>15.77833333333333</v>
+        <v>0.04277777777777778</v>
       </c>
     </row>
     <row r="176" spans="1:4">
       <c r="A176" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B176" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C176">
-        <v>60.01277777777778</v>
+        <v>57.80777777777778</v>
       </c>
       <c r="D176">
-        <v>16.90055555555556</v>
+        <v>0</v>
       </c>
     </row>
     <row r="177" spans="1:4">
       <c r="A177" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B177" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C177">
-        <v>46.45194444444444</v>
+        <v>57.80777777777778</v>
       </c>
       <c r="D177">
-        <v>17.70861111111111</v>
+        <v>0</v>
       </c>
     </row>
     <row r="178" spans="1:4">
       <c r="A178" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B178" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C178">
-        <v>50.58027777777778</v>
+        <v>47.19916666666666</v>
       </c>
       <c r="D178">
-        <v>18.90944444444444</v>
+        <v>14.58416666666667</v>
       </c>
     </row>
     <row r="179" spans="1:4">
       <c r="A179" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B179" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C179">
-        <v>48.74277777777777</v>
+        <v>46.52555555555556</v>
       </c>
       <c r="D179">
-        <v>19.35833333333333</v>
+        <v>15.15</v>
       </c>
     </row>
     <row r="180" spans="1:4">
       <c r="A180" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B180" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C180">
-        <v>15.64333333333333</v>
+        <v>53.69166666666667</v>
       </c>
       <c r="D180">
-        <v>16.58638888888889</v>
+        <v>15.77833333333333</v>
       </c>
     </row>
     <row r="181" spans="1:4">
       <c r="A181" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B181" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C181">
-        <v>21.44972222222222</v>
+        <v>60.01277777777778</v>
       </c>
       <c r="D181">
-        <v>18.38194444444444</v>
+        <v>16.90055555555556</v>
       </c>
     </row>
     <row r="182" spans="1:4">
       <c r="A182" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B182" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C182">
-        <v>37.84027777777778</v>
+        <v>46.45194444444444</v>
       </c>
       <c r="D182">
-        <v>20.02055555555556</v>
+        <v>17.70861111111111</v>
       </c>
     </row>
     <row r="183" spans="1:4">
       <c r="A183" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B183" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C183">
-        <v>47.39111111111111</v>
+        <v>50.58027777777778</v>
       </c>
       <c r="D183">
-        <v>21.35583333333333</v>
+        <v>18.90944444444444</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -3094,13 +3112,13 @@
         <v>18</v>
       </c>
       <c r="B184" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="C184">
-        <v>8.33</v>
+        <v>48.74277777777777</v>
       </c>
       <c r="D184">
-        <v>2.192777777777778</v>
+        <v>19.35833333333333</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -3108,13 +3126,13 @@
         <v>18</v>
       </c>
       <c r="B185" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="C185">
-        <v>8.844444444444445</v>
+        <v>15.64333333333333</v>
       </c>
       <c r="D185">
-        <v>2.331111111111111</v>
+        <v>16.58638888888889</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -3122,13 +3140,13 @@
         <v>18</v>
       </c>
       <c r="B186" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="C186">
-        <v>10.94416666666667</v>
+        <v>21.44972222222222</v>
       </c>
       <c r="D186">
-        <v>4.110555555555556</v>
+        <v>18.38194444444444</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -3136,13 +3154,13 @@
         <v>18</v>
       </c>
       <c r="B187" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="C187">
-        <v>15.89555555555556</v>
+        <v>37.84027777777778</v>
       </c>
       <c r="D187">
-        <v>3.350555555555556</v>
+        <v>20.02055555555556</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -3150,125 +3168,125 @@
         <v>18</v>
       </c>
       <c r="B188" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="C188">
-        <v>10.23083333333333</v>
+        <v>47.39111111111111</v>
       </c>
       <c r="D188">
-        <v>3.207777777777778</v>
+        <v>21.35583333333333</v>
       </c>
     </row>
     <row r="189" spans="1:4">
       <c r="A189" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B189" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C189">
-        <v>9.493611111111111</v>
+        <v>8.33</v>
       </c>
       <c r="D189">
-        <v>3.830833333333334</v>
+        <v>2.192777777777778</v>
       </c>
     </row>
     <row r="190" spans="1:4">
       <c r="A190" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B190" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C190">
-        <v>11.80666666666667</v>
+        <v>8.844444444444445</v>
       </c>
       <c r="D190">
-        <v>3.837777777777778</v>
+        <v>2.331111111111111</v>
       </c>
     </row>
     <row r="191" spans="1:4">
       <c r="A191" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B191" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C191">
-        <v>12.65805555555556</v>
+        <v>10.94416666666667</v>
       </c>
       <c r="D191">
-        <v>2.376944444444444</v>
+        <v>4.110555555555556</v>
       </c>
     </row>
     <row r="192" spans="1:4">
       <c r="A192" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B192" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C192">
-        <v>11.22222222222222</v>
+        <v>15.89555555555556</v>
       </c>
       <c r="D192">
-        <v>2.608055555555556</v>
+        <v>3.350555555555556</v>
       </c>
     </row>
     <row r="193" spans="1:4">
       <c r="A193" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B193" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C193">
-        <v>5.414444444444444</v>
+        <v>10.23083333333333</v>
       </c>
       <c r="D193">
-        <v>4.072222222222222</v>
+        <v>3.207777777777778</v>
       </c>
     </row>
     <row r="194" spans="1:4">
       <c r="A194" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B194" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C194">
-        <v>2.246666666666667</v>
+        <v>9.493611111111111</v>
       </c>
       <c r="D194">
-        <v>3.372777777777778</v>
+        <v>3.830833333333334</v>
       </c>
     </row>
     <row r="195" spans="1:4">
       <c r="A195" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B195" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C195">
-        <v>2.540277777777778</v>
+        <v>11.80666666666667</v>
       </c>
       <c r="D195">
-        <v>3.595833333333333</v>
+        <v>3.837777777777778</v>
       </c>
     </row>
     <row r="196" spans="1:4">
       <c r="A196" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B196" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C196">
-        <v>7.815</v>
+        <v>12.65805555555556</v>
       </c>
       <c r="D196">
-        <v>4.152222222222222</v>
+        <v>2.376944444444444</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -3276,13 +3294,13 @@
         <v>19</v>
       </c>
       <c r="B197" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="C197">
-        <v>38.75888888888889</v>
+        <v>11.22222222222222</v>
       </c>
       <c r="D197">
-        <v>29.29777777777778</v>
+        <v>2.608055555555556</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -3290,13 +3308,13 @@
         <v>19</v>
       </c>
       <c r="B198" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="C198">
-        <v>36.98277777777778</v>
+        <v>5.414444444444444</v>
       </c>
       <c r="D198">
-        <v>28.95638888888889</v>
+        <v>4.072222222222222</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -3304,13 +3322,13 @@
         <v>19</v>
       </c>
       <c r="B199" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="C199">
-        <v>35.79444444444444</v>
+        <v>2.246666666666667</v>
       </c>
       <c r="D199">
-        <v>25.57472222222222</v>
+        <v>3.372777777777778</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -3318,13 +3336,13 @@
         <v>19</v>
       </c>
       <c r="B200" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="C200">
-        <v>36.68861111111111</v>
+        <v>2.540277777777778</v>
       </c>
       <c r="D200">
-        <v>22.44638888888889</v>
+        <v>3.595833333333333</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -3332,125 +3350,125 @@
         <v>19</v>
       </c>
       <c r="B201" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="C201">
-        <v>37.76666666666667</v>
+        <v>7.815</v>
       </c>
       <c r="D201">
-        <v>22.29194444444444</v>
+        <v>4.152222222222222</v>
       </c>
     </row>
     <row r="202" spans="1:4">
       <c r="A202" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B202" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C202">
-        <v>39.31027777777778</v>
+        <v>38.75888888888889</v>
       </c>
       <c r="D202">
-        <v>25.96916666666667</v>
+        <v>29.29777777777778</v>
       </c>
     </row>
     <row r="203" spans="1:4">
       <c r="A203" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B203" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C203">
-        <v>40.78222222222222</v>
+        <v>36.98277777777778</v>
       </c>
       <c r="D203">
-        <v>27.025</v>
+        <v>28.95638888888889</v>
       </c>
     </row>
     <row r="204" spans="1:4">
       <c r="A204" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B204" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C204">
-        <v>45.74027777777778</v>
+        <v>35.79444444444444</v>
       </c>
       <c r="D204">
-        <v>31.94222222222222</v>
+        <v>25.57472222222222</v>
       </c>
     </row>
     <row r="205" spans="1:4">
       <c r="A205" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B205" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C205">
-        <v>47.33444444444444</v>
+        <v>36.68861111111111</v>
       </c>
       <c r="D205">
-        <v>31.14972222222222</v>
+        <v>22.44638888888889</v>
       </c>
     </row>
     <row r="206" spans="1:4">
       <c r="A206" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B206" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C206">
-        <v>17.83083333333333</v>
+        <v>37.76666666666667</v>
       </c>
       <c r="D206">
-        <v>28.63472222222222</v>
+        <v>22.29194444444444</v>
       </c>
     </row>
     <row r="207" spans="1:4">
       <c r="A207" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B207" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C207">
-        <v>19.46805555555556</v>
+        <v>39.31027777777778</v>
       </c>
       <c r="D207">
-        <v>29.55805555555555</v>
+        <v>25.96916666666667</v>
       </c>
     </row>
     <row r="208" spans="1:4">
       <c r="A208" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B208" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C208">
-        <v>33.92527777777778</v>
+        <v>40.78222222222222</v>
       </c>
       <c r="D208">
-        <v>28.95333333333333</v>
+        <v>27.025</v>
       </c>
     </row>
     <row r="209" spans="1:4">
       <c r="A209" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B209" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C209">
-        <v>42.93805555555556</v>
+        <v>45.74027777777778</v>
       </c>
       <c r="D209">
-        <v>26.6775</v>
+        <v>31.94222222222222</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -3458,13 +3476,13 @@
         <v>20</v>
       </c>
       <c r="B210" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="C210">
-        <v>71.07444444444444</v>
+        <v>47.33444444444444</v>
       </c>
       <c r="D210">
-        <v>45.30666666666666</v>
+        <v>31.14972222222222</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -3472,13 +3490,13 @@
         <v>20</v>
       </c>
       <c r="B211" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="C211">
-        <v>74.55361111111111</v>
+        <v>17.83083333333333</v>
       </c>
       <c r="D211">
-        <v>44.76388888888889</v>
+        <v>28.63472222222222</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -3486,13 +3504,13 @@
         <v>20</v>
       </c>
       <c r="B212" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="C212">
-        <v>75.53361111111111</v>
+        <v>19.46805555555556</v>
       </c>
       <c r="D212">
-        <v>44.23694444444445</v>
+        <v>29.55805555555555</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -3500,13 +3518,13 @@
         <v>20</v>
       </c>
       <c r="B213" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="C213">
-        <v>73.81861111111111</v>
+        <v>33.92527777777778</v>
       </c>
       <c r="D213">
-        <v>42.43194444444445</v>
+        <v>28.95333333333333</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -3514,1466 +3532,1466 @@
         <v>20</v>
       </c>
       <c r="B214" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="C214">
-        <v>74.43111111111111</v>
+        <v>42.93805555555556</v>
       </c>
       <c r="D214">
-        <v>47.16583333333333</v>
+        <v>26.6775</v>
       </c>
     </row>
     <row r="215" spans="1:4">
       <c r="A215" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B215" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="C215">
-        <v>77.82416666666667</v>
+        <v>47.33444444444444</v>
       </c>
       <c r="D215">
-        <v>49.03</v>
+        <v>31.14972222222222</v>
       </c>
     </row>
     <row r="216" spans="1:4">
       <c r="A216" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B216" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="C216">
-        <v>81.48583333333333</v>
+        <v>17.83083333333333</v>
       </c>
       <c r="D216">
-        <v>46.97861111111111</v>
+        <v>28.63472222222222</v>
       </c>
     </row>
     <row r="217" spans="1:4">
       <c r="A217" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B217" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="C217">
-        <v>83.79527777777778</v>
+        <v>19.46805555555556</v>
       </c>
       <c r="D217">
-        <v>49.43305555555555</v>
+        <v>29.55805555555555</v>
       </c>
     </row>
     <row r="218" spans="1:4">
       <c r="A218" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B218" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="C218">
-        <v>84.10472222222222</v>
+        <v>33.92527777777778</v>
       </c>
       <c r="D218">
-        <v>49.65666666666667</v>
+        <v>28.95333333333333</v>
       </c>
     </row>
     <row r="219" spans="1:4">
       <c r="A219" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B219" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="C219">
-        <v>33.12833333333333</v>
+        <v>42.93805555555556</v>
       </c>
       <c r="D219">
-        <v>53.96638888888889</v>
+        <v>26.6775</v>
       </c>
     </row>
     <row r="220" spans="1:4">
       <c r="A220" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B220" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C220">
-        <v>46.12833333333333</v>
+        <v>71.07444444444444</v>
       </c>
       <c r="D220">
-        <v>53.70444444444445</v>
+        <v>45.30666666666666</v>
       </c>
     </row>
     <row r="221" spans="1:4">
       <c r="A221" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B221" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C221">
-        <v>56.31222222222222</v>
+        <v>74.55361111111111</v>
       </c>
       <c r="D221">
-        <v>52.58416666666667</v>
+        <v>44.76388888888889</v>
       </c>
     </row>
     <row r="222" spans="1:4">
       <c r="A222" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B222" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C222">
-        <v>84.56361111111111</v>
+        <v>75.53361111111111</v>
       </c>
       <c r="D222">
-        <v>47.32416666666666</v>
+        <v>44.23694444444445</v>
       </c>
     </row>
     <row r="223" spans="1:4">
       <c r="A223" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B223" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="C223">
-        <v>8.219722222222222</v>
+        <v>73.81861111111111</v>
       </c>
       <c r="D223">
-        <v>0.3052777777777778</v>
+        <v>42.43194444444445</v>
       </c>
     </row>
     <row r="224" spans="1:4">
       <c r="A224" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B224" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="C224">
-        <v>8.219722222222222</v>
+        <v>74.43111111111111</v>
       </c>
       <c r="D224">
-        <v>0.1466666666666667</v>
+        <v>47.16583333333333</v>
       </c>
     </row>
     <row r="225" spans="1:4">
       <c r="A225" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B225" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="C225">
-        <v>6.753333333333333</v>
+        <v>77.82416666666667</v>
       </c>
       <c r="D225">
-        <v>0.3244444444444444</v>
+        <v>49.03</v>
       </c>
     </row>
     <row r="226" spans="1:4">
       <c r="A226" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B226" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="C226">
-        <v>2.571388888888889</v>
+        <v>81.48583333333333</v>
       </c>
       <c r="D226">
-        <v>0.1983333333333333</v>
+        <v>46.97861111111111</v>
       </c>
     </row>
     <row r="227" spans="1:4">
       <c r="A227" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B227" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="C227">
-        <v>3.683611111111111</v>
+        <v>83.79527777777778</v>
       </c>
       <c r="D227">
-        <v>0.04388888888888889</v>
+        <v>49.43305555555555</v>
       </c>
     </row>
     <row r="228" spans="1:4">
       <c r="A228" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B228" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="C228">
-        <v>8.631388888888889</v>
+        <v>84.10472222222222</v>
       </c>
       <c r="D228">
-        <v>0</v>
+        <v>49.65666666666667</v>
       </c>
     </row>
     <row r="229" spans="1:4">
       <c r="A229" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B229" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="C229">
-        <v>9.331111111111111</v>
+        <v>33.12833333333333</v>
       </c>
       <c r="D229">
-        <v>0.08888888888888889</v>
+        <v>53.96638888888889</v>
       </c>
     </row>
     <row r="230" spans="1:4">
       <c r="A230" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B230" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="C230">
-        <v>8.256388888888889</v>
+        <v>46.12833333333333</v>
       </c>
       <c r="D230">
-        <v>0.5519444444444445</v>
+        <v>53.70444444444445</v>
       </c>
     </row>
     <row r="231" spans="1:4">
       <c r="A231" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B231" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="C231">
-        <v>8.641111111111112</v>
+        <v>56.31222222222222</v>
       </c>
       <c r="D231">
-        <v>0.1480555555555556</v>
+        <v>52.58416666666667</v>
       </c>
     </row>
     <row r="232" spans="1:4">
       <c r="A232" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B232" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="C232">
-        <v>4.804166666666666</v>
+        <v>84.56361111111111</v>
       </c>
       <c r="D232">
-        <v>0.06944444444444445</v>
+        <v>47.32416666666666</v>
       </c>
     </row>
     <row r="233" spans="1:4">
       <c r="A233" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B233" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C233">
-        <v>5.882777777777778</v>
+        <v>8.219722222222222</v>
       </c>
       <c r="D233">
-        <v>0.5805555555555556</v>
+        <v>0.3052777777777778</v>
       </c>
     </row>
     <row r="234" spans="1:4">
       <c r="A234" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B234" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C234">
-        <v>6.680555555555555</v>
+        <v>8.219722222222222</v>
       </c>
       <c r="D234">
-        <v>0.04638888888888889</v>
+        <v>0.1466666666666667</v>
       </c>
     </row>
     <row r="235" spans="1:4">
       <c r="A235" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B235" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C235">
-        <v>7.816111111111111</v>
+        <v>6.753333333333333</v>
       </c>
       <c r="D235">
-        <v>0.6430555555555556</v>
+        <v>0.3244444444444444</v>
       </c>
     </row>
     <row r="236" spans="1:4">
       <c r="A236" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B236" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="C236">
-        <v>0.5022222222222222</v>
+        <v>2.571388888888889</v>
       </c>
       <c r="D236">
-        <v>0.9313888888888889</v>
+        <v>0.1983333333333333</v>
       </c>
     </row>
     <row r="237" spans="1:4">
       <c r="A237" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B237" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="C237">
-        <v>2.0825</v>
+        <v>3.683611111111111</v>
       </c>
       <c r="D237">
-        <v>4.0175</v>
+        <v>0.04388888888888889</v>
       </c>
     </row>
     <row r="238" spans="1:4">
       <c r="A238" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B238" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="C238">
-        <v>1.555833333333333</v>
+        <v>8.631388888888889</v>
       </c>
       <c r="D238">
-        <v>2.704444444444444</v>
+        <v>0</v>
       </c>
     </row>
     <row r="239" spans="1:4">
       <c r="A239" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B239" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="C239">
-        <v>1.188333333333333</v>
+        <v>9.331111111111111</v>
       </c>
       <c r="D239">
-        <v>1.066111111111111</v>
+        <v>0.08888888888888889</v>
       </c>
     </row>
     <row r="240" spans="1:4">
       <c r="A240" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B240" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="C240">
-        <v>0.6247222222222222</v>
+        <v>8.256388888888889</v>
       </c>
       <c r="D240">
-        <v>0.9313888888888889</v>
+        <v>0.5519444444444445</v>
       </c>
     </row>
     <row r="241" spans="1:4">
       <c r="A241" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B241" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="C241">
-        <v>0.6491666666666667</v>
+        <v>8.641111111111112</v>
       </c>
       <c r="D241">
-        <v>0.9538888888888889</v>
+        <v>0.1480555555555556</v>
       </c>
     </row>
     <row r="242" spans="1:4">
       <c r="A242" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B242" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="C242">
-        <v>0.6875</v>
+        <v>4.804166666666666</v>
       </c>
       <c r="D242">
-        <v>2.465277777777778</v>
+        <v>0.06944444444444445</v>
       </c>
     </row>
     <row r="243" spans="1:4">
       <c r="A243" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B243" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="C243">
-        <v>0.5686111111111111</v>
+        <v>5.882777777777778</v>
       </c>
       <c r="D243">
-        <v>3.149166666666666</v>
+        <v>0.5805555555555556</v>
       </c>
     </row>
     <row r="244" spans="1:4">
       <c r="A244" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B244" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="C244">
-        <v>0.6036111111111111</v>
+        <v>6.680555555555555</v>
       </c>
       <c r="D244">
-        <v>3.266388888888889</v>
+        <v>0.04638888888888889</v>
       </c>
     </row>
     <row r="245" spans="1:4">
       <c r="A245" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B245" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="C245">
-        <v>0.2116666666666667</v>
+        <v>7.816111111111111</v>
       </c>
       <c r="D245">
-        <v>1.088888888888889</v>
+        <v>0.6430555555555556</v>
       </c>
     </row>
     <row r="246" spans="1:4">
       <c r="A246" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B246" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C246">
-        <v>0.5252777777777777</v>
+        <v>0.5022222222222222</v>
       </c>
       <c r="D246">
-        <v>3.411111111111111</v>
+        <v>0.9313888888888889</v>
       </c>
     </row>
     <row r="247" spans="1:4">
       <c r="A247" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B247" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C247">
-        <v>0.7352777777777778</v>
+        <v>2.0825</v>
       </c>
       <c r="D247">
-        <v>2.876944444444444</v>
+        <v>4.0175</v>
       </c>
     </row>
     <row r="248" spans="1:4">
       <c r="A248" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B248" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C248">
-        <v>1.201944444444444</v>
+        <v>1.555833333333333</v>
       </c>
       <c r="D248">
-        <v>3.201666666666667</v>
+        <v>2.704444444444444</v>
       </c>
     </row>
     <row r="249" spans="1:4">
       <c r="A249" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B249" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="C249">
-        <v>17.65277777777778</v>
+        <v>1.188333333333333</v>
       </c>
       <c r="D249">
-        <v>10.85694444444444</v>
+        <v>1.066111111111111</v>
       </c>
     </row>
     <row r="250" spans="1:4">
       <c r="A250" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B250" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="C250">
-        <v>18.68194444444444</v>
+        <v>0.6247222222222222</v>
       </c>
       <c r="D250">
-        <v>10.91361111111111</v>
+        <v>0.9313888888888889</v>
       </c>
     </row>
     <row r="251" spans="1:4">
       <c r="A251" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B251" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="C251">
-        <v>19.55166666666667</v>
+        <v>0.6491666666666667</v>
       </c>
       <c r="D251">
-        <v>9.529722222222222</v>
+        <v>0.9538888888888889</v>
       </c>
     </row>
     <row r="252" spans="1:4">
       <c r="A252" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B252" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="C252">
-        <v>21.23</v>
+        <v>0.6875</v>
       </c>
       <c r="D252">
-        <v>9.654722222222222</v>
+        <v>2.465277777777778</v>
       </c>
     </row>
     <row r="253" spans="1:4">
       <c r="A253" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B253" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="C253">
-        <v>22.94472222222222</v>
+        <v>0.5686111111111111</v>
       </c>
       <c r="D253">
-        <v>9.976944444444445</v>
+        <v>3.149166666666666</v>
       </c>
     </row>
     <row r="254" spans="1:4">
       <c r="A254" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B254" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="C254">
-        <v>24.23111111111111</v>
+        <v>0.6036111111111111</v>
       </c>
       <c r="D254">
-        <v>10.50805555555556</v>
+        <v>3.266388888888889</v>
       </c>
     </row>
     <row r="255" spans="1:4">
       <c r="A255" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B255" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="C255">
-        <v>26.40277777777778</v>
+        <v>0.2116666666666667</v>
       </c>
       <c r="D255">
-        <v>9.323611111111111</v>
+        <v>1.088888888888889</v>
       </c>
     </row>
     <row r="256" spans="1:4">
       <c r="A256" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B256" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="C256">
-        <v>27.37805555555556</v>
+        <v>0.5252777777777777</v>
       </c>
       <c r="D256">
-        <v>8.24</v>
+        <v>3.411111111111111</v>
       </c>
     </row>
     <row r="257" spans="1:4">
       <c r="A257" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B257" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="C257">
-        <v>27.88138888888889</v>
+        <v>0.7352777777777778</v>
       </c>
       <c r="D257">
-        <v>9.262499999999999</v>
+        <v>2.876944444444444</v>
       </c>
     </row>
     <row r="258" spans="1:4">
       <c r="A258" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B258" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="C258">
-        <v>11.13083333333333</v>
+        <v>1.201944444444444</v>
       </c>
       <c r="D258">
-        <v>1.836944444444444</v>
+        <v>3.201666666666667</v>
       </c>
     </row>
     <row r="259" spans="1:4">
       <c r="A259" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B259" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C259">
-        <v>17.93277777777778</v>
+        <v>17.65277777777778</v>
       </c>
       <c r="D259">
-        <v>4.953611111111111</v>
+        <v>10.85694444444444</v>
       </c>
     </row>
     <row r="260" spans="1:4">
       <c r="A260" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B260" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C260">
-        <v>26.82333333333333</v>
+        <v>18.68194444444444</v>
       </c>
       <c r="D260">
-        <v>6.8</v>
+        <v>10.91361111111111</v>
       </c>
     </row>
     <row r="261" spans="1:4">
       <c r="A261" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B261" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C261">
-        <v>28.36694444444445</v>
+        <v>19.55166666666667</v>
       </c>
       <c r="D261">
-        <v>6.111388888888889</v>
+        <v>9.529722222222222</v>
       </c>
     </row>
     <row r="262" spans="1:4">
       <c r="A262" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B262" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="C262">
-        <v>6.602777777777778</v>
+        <v>21.23</v>
       </c>
       <c r="D262">
-        <v>1.554166666666667</v>
+        <v>9.654722222222222</v>
       </c>
     </row>
     <row r="263" spans="1:4">
       <c r="A263" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B263" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="C263">
-        <v>5.928888888888889</v>
+        <v>22.94472222222222</v>
       </c>
       <c r="D263">
-        <v>1.554166666666667</v>
+        <v>9.976944444444445</v>
       </c>
     </row>
     <row r="264" spans="1:4">
       <c r="A264" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B264" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="C264">
-        <v>6.749722222222222</v>
+        <v>24.23111111111111</v>
       </c>
       <c r="D264">
-        <v>1.554166666666667</v>
+        <v>10.50805555555556</v>
       </c>
     </row>
     <row r="265" spans="1:4">
       <c r="A265" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B265" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="C265">
-        <v>7.423611111111111</v>
+        <v>26.40277777777778</v>
       </c>
       <c r="D265">
-        <v>1.554166666666667</v>
+        <v>9.323611111111111</v>
       </c>
     </row>
     <row r="266" spans="1:4">
       <c r="A266" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B266" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="C266">
-        <v>7.7175</v>
+        <v>27.37805555555556</v>
       </c>
       <c r="D266">
-        <v>1.554166666666667</v>
+        <v>8.24</v>
       </c>
     </row>
     <row r="267" spans="1:4">
       <c r="A267" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B267" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="C267">
-        <v>7.864444444444445</v>
+        <v>27.88138888888889</v>
       </c>
       <c r="D267">
-        <v>1.554166666666667</v>
+        <v>9.262499999999999</v>
       </c>
     </row>
     <row r="268" spans="1:4">
       <c r="A268" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B268" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="C268">
-        <v>8.305555555555555</v>
+        <v>11.13083333333333</v>
       </c>
       <c r="D268">
-        <v>1.557222222222222</v>
+        <v>1.836944444444444</v>
       </c>
     </row>
     <row r="269" spans="1:4">
       <c r="A269" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B269" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="C269">
-        <v>8.989722222222222</v>
+        <v>17.93277777777778</v>
       </c>
       <c r="D269">
-        <v>1.557222222222222</v>
+        <v>4.953611111111111</v>
       </c>
     </row>
     <row r="270" spans="1:4">
       <c r="A270" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B270" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="C270">
-        <v>9.484722222222222</v>
+        <v>26.82333333333333</v>
       </c>
       <c r="D270">
-        <v>1.563055555555556</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="271" spans="1:4">
       <c r="A271" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B271" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="C271">
-        <v>3.410833333333333</v>
+        <v>28.36694444444445</v>
       </c>
       <c r="D271">
-        <v>1.563055555555556</v>
+        <v>6.111388888888889</v>
       </c>
     </row>
     <row r="272" spans="1:4">
       <c r="A272" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B272" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C272">
-        <v>4.5975</v>
+        <v>6.602777777777778</v>
       </c>
       <c r="D272">
-        <v>1.563055555555556</v>
+        <v>1.554166666666667</v>
       </c>
     </row>
     <row r="273" spans="1:4">
       <c r="A273" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B273" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C273">
-        <v>7.714444444444444</v>
+        <v>5.928888888888889</v>
       </c>
       <c r="D273">
-        <v>1.563055555555556</v>
+        <v>1.554166666666667</v>
       </c>
     </row>
     <row r="274" spans="1:4">
       <c r="A274" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B274" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C274">
-        <v>9.737222222222222</v>
+        <v>6.749722222222222</v>
       </c>
       <c r="D274">
-        <v>1.563055555555556</v>
+        <v>1.554166666666667</v>
       </c>
     </row>
     <row r="275" spans="1:4">
       <c r="A275" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B275" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="C275">
-        <v>0.1225</v>
+        <v>7.423611111111111</v>
       </c>
       <c r="D275">
-        <v>0.05388888888888889</v>
+        <v>1.554166666666667</v>
       </c>
     </row>
     <row r="276" spans="1:4">
       <c r="A276" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B276" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="C276">
-        <v>0.5197222222222222</v>
+        <v>7.7175</v>
       </c>
       <c r="D276">
-        <v>0.09888888888888889</v>
+        <v>1.554166666666667</v>
       </c>
     </row>
     <row r="277" spans="1:4">
       <c r="A277" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B277" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="C277">
-        <v>0.2697222222222222</v>
+        <v>7.864444444444445</v>
       </c>
       <c r="D277">
-        <v>0.1908333333333333</v>
+        <v>1.554166666666667</v>
       </c>
     </row>
     <row r="278" spans="1:4">
       <c r="A278" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B278" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="C278">
-        <v>0.2697222222222222</v>
+        <v>8.305555555555555</v>
       </c>
       <c r="D278">
-        <v>0.2233333333333333</v>
+        <v>1.557222222222222</v>
       </c>
     </row>
     <row r="279" spans="1:4">
       <c r="A279" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B279" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="C279">
-        <v>0.9066666666666666</v>
+        <v>8.989722222222222</v>
       </c>
       <c r="D279">
-        <v>0</v>
+        <v>1.557222222222222</v>
       </c>
     </row>
     <row r="280" spans="1:4">
       <c r="A280" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B280" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="C280">
-        <v>0.7719444444444444</v>
+        <v>9.484722222222222</v>
       </c>
       <c r="D280">
-        <v>0</v>
+        <v>1.563055555555556</v>
       </c>
     </row>
     <row r="281" spans="1:4">
       <c r="A281" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B281" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="C281">
-        <v>0.3597222222222222</v>
+        <v>3.410833333333333</v>
       </c>
       <c r="D281">
-        <v>0</v>
+        <v>1.563055555555556</v>
       </c>
     </row>
     <row r="282" spans="1:4">
       <c r="A282" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B282" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="C282">
-        <v>0.985</v>
+        <v>4.5975</v>
       </c>
       <c r="D282">
-        <v>0</v>
+        <v>1.563055555555556</v>
       </c>
     </row>
     <row r="283" spans="1:4">
       <c r="A283" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B283" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="C283">
-        <v>1.001944444444445</v>
+        <v>7.714444444444444</v>
       </c>
       <c r="D283">
-        <v>0</v>
+        <v>1.563055555555556</v>
       </c>
     </row>
     <row r="284" spans="1:4">
       <c r="A284" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B284" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="C284">
-        <v>1.029166666666667</v>
+        <v>9.737222222222222</v>
       </c>
       <c r="D284">
-        <v>0</v>
+        <v>1.563055555555556</v>
       </c>
     </row>
     <row r="285" spans="1:4">
       <c r="A285" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B285" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C285">
-        <v>1.153055555555556</v>
+        <v>0.1225</v>
       </c>
       <c r="D285">
-        <v>0</v>
+        <v>0.05388888888888889</v>
       </c>
     </row>
     <row r="286" spans="1:4">
       <c r="A286" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B286" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C286">
-        <v>1.204166666666667</v>
+        <v>0.5197222222222222</v>
       </c>
       <c r="D286">
-        <v>0</v>
+        <v>0.09888888888888889</v>
       </c>
     </row>
     <row r="287" spans="1:4">
       <c r="A287" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B287" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C287">
-        <v>1.254166666666667</v>
+        <v>0.2697222222222222</v>
       </c>
       <c r="D287">
-        <v>0</v>
+        <v>0.1908333333333333</v>
       </c>
     </row>
     <row r="288" spans="1:4">
       <c r="A288" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B288" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="C288">
-        <v>4.703888888888889</v>
+        <v>0.2697222222222222</v>
       </c>
       <c r="D288">
-        <v>4.578333333333333</v>
+        <v>0.2233333333333333</v>
       </c>
     </row>
     <row r="289" spans="1:4">
       <c r="A289" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B289" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="C289">
-        <v>4.998055555555555</v>
+        <v>0.9066666666666666</v>
       </c>
       <c r="D289">
-        <v>4.624166666666667</v>
+        <v>0</v>
       </c>
     </row>
     <row r="290" spans="1:4">
       <c r="A290" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B290" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="C290">
-        <v>4.152777777777778</v>
+        <v>0.7719444444444444</v>
       </c>
       <c r="D290">
-        <v>4.246388888888889</v>
+        <v>0</v>
       </c>
     </row>
     <row r="291" spans="1:4">
       <c r="A291" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B291" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="C291">
-        <v>3.699444444444445</v>
+        <v>0.3597222222222222</v>
       </c>
       <c r="D291">
-        <v>4.315277777777778</v>
+        <v>0</v>
       </c>
     </row>
     <row r="292" spans="1:4">
       <c r="A292" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B292" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="C292">
-        <v>4.152777777777778</v>
+        <v>0.985</v>
       </c>
       <c r="D292">
-        <v>4.292222222222223</v>
+        <v>0</v>
       </c>
     </row>
     <row r="293" spans="1:4">
       <c r="A293" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B293" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="C293">
-        <v>5.193888888888889</v>
+        <v>1.001944444444445</v>
       </c>
       <c r="D293">
-        <v>3.5825</v>
+        <v>0</v>
       </c>
     </row>
     <row r="294" spans="1:4">
       <c r="A294" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B294" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="C294">
-        <v>6.183611111111111</v>
+        <v>1.029166666666667</v>
       </c>
       <c r="D294">
-        <v>3.608888888888889</v>
+        <v>0</v>
       </c>
     </row>
     <row r="295" spans="1:4">
       <c r="A295" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B295" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="C295">
-        <v>7.9675</v>
+        <v>1.153055555555556</v>
       </c>
       <c r="D295">
-        <v>3.79</v>
+        <v>0</v>
       </c>
     </row>
     <row r="296" spans="1:4">
       <c r="A296" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B296" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="C296">
-        <v>7.991944444444444</v>
+        <v>1.204166666666667</v>
       </c>
       <c r="D296">
-        <v>3.926388888888889</v>
+        <v>0</v>
       </c>
     </row>
     <row r="297" spans="1:4">
       <c r="A297" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B297" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="C297">
-        <v>3.724722222222222</v>
+        <v>1.254166666666667</v>
       </c>
       <c r="D297">
-        <v>2.944166666666667</v>
+        <v>0</v>
       </c>
     </row>
     <row r="298" spans="1:4">
       <c r="A298" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B298" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C298">
-        <v>5.591666666666667</v>
+        <v>0.5252777777777777</v>
       </c>
       <c r="D298">
-        <v>2.443888888888889</v>
+        <v>0</v>
       </c>
     </row>
     <row r="299" spans="1:4">
       <c r="A299" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B299" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="C299">
-        <v>7.243055555555555</v>
+        <v>0.5430555555555555</v>
       </c>
       <c r="D299">
-        <v>2.177222222222222</v>
+        <v>0</v>
       </c>
     </row>
     <row r="300" spans="1:4">
       <c r="A300" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B300" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C300">
-        <v>7.11</v>
+        <v>0.5538888888888889</v>
       </c>
       <c r="D300">
-        <v>2.445277777777778</v>
+        <v>0</v>
       </c>
     </row>
     <row r="301" spans="1:4">
       <c r="A301" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B301" t="s">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="C301">
-        <v>9.224166666666667</v>
+        <v>0.7966666666666666</v>
       </c>
       <c r="D301">
-        <v>1.930277777777778</v>
+        <v>0</v>
       </c>
     </row>
     <row r="302" spans="1:4">
       <c r="A302" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B302" t="s">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="C302">
-        <v>8.097222222222221</v>
+        <v>0.4044444444444444</v>
       </c>
       <c r="D302">
-        <v>2.423888888888889</v>
+        <v>0</v>
       </c>
     </row>
     <row r="303" spans="1:4">
       <c r="A303" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B303" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="C303">
-        <v>8.834722222222222</v>
+        <v>4.703888888888889</v>
       </c>
       <c r="D303">
-        <v>0</v>
+        <v>4.578333333333333</v>
       </c>
     </row>
     <row r="304" spans="1:4">
       <c r="A304" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B304" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C304">
-        <v>9.811111111111112</v>
+        <v>4.998055555555555</v>
       </c>
       <c r="D304">
-        <v>0</v>
+        <v>4.624166666666667</v>
       </c>
     </row>
     <row r="305" spans="1:4">
       <c r="A305" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B305" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C305">
-        <v>10.28638888888889</v>
+        <v>4.152777777777778</v>
       </c>
       <c r="D305">
-        <v>0</v>
+        <v>4.246388888888889</v>
       </c>
     </row>
     <row r="306" spans="1:4">
       <c r="A306" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B306" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C306">
-        <v>11.6375</v>
+        <v>3.699444444444445</v>
       </c>
       <c r="D306">
-        <v>0</v>
+        <v>4.315277777777778</v>
       </c>
     </row>
     <row r="307" spans="1:4">
       <c r="A307" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B307" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="C307">
-        <v>8.300555555555556</v>
+        <v>4.152777777777778</v>
       </c>
       <c r="D307">
-        <v>0</v>
+        <v>4.292222222222223</v>
       </c>
     </row>
     <row r="308" spans="1:4">
       <c r="A308" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B308" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C308">
-        <v>8.294166666666667</v>
+        <v>5.193888888888889</v>
       </c>
       <c r="D308">
-        <v>5.326111111111111</v>
+        <v>3.5825</v>
       </c>
     </row>
     <row r="309" spans="1:4">
       <c r="A309" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B309" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C309">
-        <v>8.652222222222223</v>
+        <v>6.183611111111111</v>
       </c>
       <c r="D309">
-        <v>4.897222222222222</v>
+        <v>3.608888888888889</v>
       </c>
     </row>
     <row r="310" spans="1:4">
       <c r="A310" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B310" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C310">
-        <v>3.089444444444445</v>
+        <v>7.9675</v>
       </c>
       <c r="D310">
-        <v>2.796111111111111</v>
+        <v>3.79</v>
       </c>
     </row>
     <row r="311" spans="1:4">
       <c r="A311" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B311" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C311">
-        <v>3.726666666666667</v>
+        <v>7.991944444444444</v>
       </c>
       <c r="D311">
-        <v>3.046388888888889</v>
+        <v>3.926388888888889</v>
       </c>
     </row>
     <row r="312" spans="1:4">
       <c r="A312" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B312" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="C312">
-        <v>5.495277777777778</v>
+        <v>3.724722222222222</v>
       </c>
       <c r="D312">
-        <v>2.928611111111111</v>
+        <v>2.944166666666667</v>
       </c>
     </row>
     <row r="313" spans="1:4">
       <c r="A313" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B313" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C313">
-        <v>6.546111111111111</v>
+        <v>5.591666666666667</v>
       </c>
       <c r="D313">
-        <v>1.485555555555556</v>
+        <v>2.443888888888889</v>
       </c>
     </row>
     <row r="314" spans="1:4">
       <c r="A314" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B314" t="s">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="C314">
-        <v>0.6002777777777778</v>
+        <v>7.243055555555555</v>
       </c>
       <c r="D314">
-        <v>0</v>
+        <v>2.177222222222222</v>
       </c>
     </row>
     <row r="315" spans="1:4">
       <c r="A315" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B315" t="s">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="C315">
-        <v>0.5758333333333333</v>
+        <v>7.11</v>
       </c>
       <c r="D315">
-        <v>0</v>
+        <v>2.445277777777778</v>
       </c>
     </row>
     <row r="316" spans="1:4">
       <c r="A316" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B316" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="C316">
-        <v>0.5266666666666666</v>
+        <v>9.224166666666667</v>
       </c>
       <c r="D316">
-        <v>0</v>
+        <v>1.930277777777778</v>
       </c>
     </row>
     <row r="317" spans="1:4">
       <c r="A317" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B317" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C317">
-        <v>0.49</v>
+        <v>8.097222222222221</v>
       </c>
       <c r="D317">
-        <v>0</v>
+        <v>2.423888888888889</v>
       </c>
     </row>
     <row r="318" spans="1:4">
       <c r="A318" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B318" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C318">
-        <v>0.6125</v>
+        <v>8.834722222222222</v>
       </c>
       <c r="D318">
         <v>0</v>
@@ -4981,13 +4999,13 @@
     </row>
     <row r="319" spans="1:4">
       <c r="A319" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B319" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C319">
-        <v>0.5022222222222222</v>
+        <v>9.811111111111112</v>
       </c>
       <c r="D319">
         <v>0</v>
@@ -4995,13 +5013,13 @@
     </row>
     <row r="320" spans="1:4">
       <c r="A320" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B320" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="C320">
-        <v>0.3841666666666667</v>
+        <v>10.28638888888889</v>
       </c>
       <c r="D320">
         <v>0</v>
@@ -5009,13 +5027,13 @@
     </row>
     <row r="321" spans="1:4">
       <c r="A321" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B321" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C321">
-        <v>0.3858333333333333</v>
+        <v>11.6375</v>
       </c>
       <c r="D321">
         <v>0</v>
@@ -5023,13 +5041,13 @@
     </row>
     <row r="322" spans="1:4">
       <c r="A322" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B322" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C322">
-        <v>0.2163888888888889</v>
+        <v>8.300555555555556</v>
       </c>
       <c r="D322">
         <v>0</v>
@@ -5037,1695 +5055,2115 @@
     </row>
     <row r="323" spans="1:4">
       <c r="A323" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B323" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C323">
-        <v>0.2619444444444444</v>
+        <v>8.294166666666667</v>
       </c>
       <c r="D323">
-        <v>0</v>
+        <v>5.326111111111111</v>
       </c>
     </row>
     <row r="324" spans="1:4">
       <c r="A324" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B324" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C324">
-        <v>0.2669444444444444</v>
+        <v>8.652222222222223</v>
       </c>
       <c r="D324">
-        <v>0</v>
+        <v>4.897222222222222</v>
       </c>
     </row>
     <row r="325" spans="1:4">
       <c r="A325" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B325" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="C325">
-        <v>0.3594444444444445</v>
+        <v>3.089444444444445</v>
       </c>
       <c r="D325">
-        <v>0</v>
+        <v>2.796111111111111</v>
       </c>
     </row>
     <row r="326" spans="1:4">
       <c r="A326" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B326" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C326">
-        <v>0.3875</v>
+        <v>3.726666666666667</v>
       </c>
       <c r="D326">
-        <v>0</v>
+        <v>3.046388888888889</v>
       </c>
     </row>
     <row r="327" spans="1:4">
       <c r="A327" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B327" t="s">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="C327">
-        <v>76.64833333333333</v>
+        <v>5.495277777777778</v>
       </c>
       <c r="D327">
-        <v>35.11305555555555</v>
+        <v>2.928611111111111</v>
       </c>
     </row>
     <row r="328" spans="1:4">
       <c r="A328" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B328" t="s">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="C328">
-        <v>80.90861111111111</v>
+        <v>6.546111111111111</v>
       </c>
       <c r="D328">
-        <v>43.24305555555556</v>
+        <v>1.485555555555556</v>
       </c>
     </row>
     <row r="329" spans="1:4">
       <c r="A329" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B329" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="C329">
-        <v>74.14472222222223</v>
+        <v>0.6002777777777778</v>
       </c>
       <c r="D329">
-        <v>59.66194444444444</v>
+        <v>0</v>
       </c>
     </row>
     <row r="330" spans="1:4">
       <c r="A330" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B330" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C330">
-        <v>68.93722222222222</v>
+        <v>0.5758333333333333</v>
       </c>
       <c r="D330">
-        <v>179.4602777777778</v>
+        <v>0</v>
       </c>
     </row>
     <row r="331" spans="1:4">
       <c r="A331" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B331" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C331">
-        <v>61.8075</v>
+        <v>0.5266666666666666</v>
       </c>
       <c r="D331">
-        <v>201.7544444444444</v>
+        <v>0</v>
       </c>
     </row>
     <row r="332" spans="1:4">
       <c r="A332" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B332" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C332">
-        <v>59.50416666666667</v>
+        <v>0.49</v>
       </c>
       <c r="D332">
-        <v>192.0925</v>
+        <v>0</v>
       </c>
     </row>
     <row r="333" spans="1:4">
       <c r="A333" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B333" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="C333">
-        <v>66.14611111111111</v>
+        <v>0.6125</v>
       </c>
       <c r="D333">
-        <v>202.5288888888889</v>
+        <v>0</v>
       </c>
     </row>
     <row r="334" spans="1:4">
       <c r="A334" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B334" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C334">
-        <v>68.33222222222223</v>
+        <v>0.5022222222222222</v>
       </c>
       <c r="D334">
-        <v>138.0383333333333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="335" spans="1:4">
       <c r="A335" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B335" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C335">
-        <v>39.34722222222222</v>
+        <v>0.3841666666666667</v>
       </c>
       <c r="D335">
-        <v>126.8880555555556</v>
+        <v>0</v>
       </c>
     </row>
     <row r="336" spans="1:4">
       <c r="A336" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B336" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C336">
-        <v>16.48944444444444</v>
+        <v>0.3858333333333333</v>
       </c>
       <c r="D336">
-        <v>79.93972222222222</v>
+        <v>0</v>
       </c>
     </row>
     <row r="337" spans="1:4">
       <c r="A337" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B337" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C337">
-        <v>20.13666666666667</v>
+        <v>0.2163888888888889</v>
       </c>
       <c r="D337">
-        <v>70.97750000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="338" spans="1:4">
       <c r="A338" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B338" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="C338">
-        <v>18.49861111111111</v>
+        <v>0.2619444444444444</v>
       </c>
       <c r="D338">
-        <v>77.7475</v>
+        <v>0</v>
       </c>
     </row>
     <row r="339" spans="1:4">
       <c r="A339" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B339" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C339">
-        <v>22.11</v>
+        <v>0.2669444444444444</v>
       </c>
       <c r="D339">
-        <v>81.71250000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="340" spans="1:4">
       <c r="A340" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B340" t="s">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="C340">
-        <v>24.61027777777778</v>
+        <v>0.3594444444444445</v>
       </c>
       <c r="D340">
-        <v>35.88861111111111</v>
+        <v>0</v>
       </c>
     </row>
     <row r="341" spans="1:4">
       <c r="A341" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B341" t="s">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="C341">
-        <v>25.49222222222222</v>
+        <v>0.3875</v>
       </c>
       <c r="D341">
-        <v>37.95361111111111</v>
+        <v>0</v>
       </c>
     </row>
     <row r="342" spans="1:4">
       <c r="A342" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B342" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="C342">
-        <v>22.89527777777778</v>
+        <v>76.64833333333333</v>
       </c>
       <c r="D342">
-        <v>38.425</v>
+        <v>35.11305555555555</v>
       </c>
     </row>
     <row r="343" spans="1:4">
       <c r="A343" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B343" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C343">
-        <v>28.10138888888889</v>
+        <v>80.90861111111111</v>
       </c>
       <c r="D343">
-        <v>36.18055555555556</v>
+        <v>43.24305555555556</v>
       </c>
     </row>
     <row r="344" spans="1:4">
       <c r="A344" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B344" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C344">
-        <v>32.31555555555556</v>
+        <v>74.14472222222223</v>
       </c>
       <c r="D344">
-        <v>35.67555555555555</v>
+        <v>59.66194444444444</v>
       </c>
     </row>
     <row r="345" spans="1:4">
       <c r="A345" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B345" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C345">
-        <v>34.33666666666667</v>
+        <v>68.93722222222222</v>
       </c>
       <c r="D345">
-        <v>38.75027777777778</v>
+        <v>179.4602777777778</v>
       </c>
     </row>
     <row r="346" spans="1:4">
       <c r="A346" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B346" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="C346">
-        <v>38.72222222222222</v>
+        <v>61.8075</v>
       </c>
       <c r="D346">
-        <v>37.31388888888889</v>
+        <v>201.7544444444444</v>
       </c>
     </row>
     <row r="347" spans="1:4">
       <c r="A347" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B347" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C347">
-        <v>41.90722222222222</v>
+        <v>59.50416666666667</v>
       </c>
       <c r="D347">
-        <v>39.47972222222222</v>
+        <v>192.0925</v>
       </c>
     </row>
     <row r="348" spans="1:4">
       <c r="A348" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B348" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C348">
-        <v>41.30694444444445</v>
+        <v>66.14611111111111</v>
       </c>
       <c r="D348">
-        <v>37.68944444444445</v>
+        <v>202.5288888888889</v>
       </c>
     </row>
     <row r="349" spans="1:4">
       <c r="A349" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B349" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C349">
-        <v>13.3525</v>
+        <v>68.33222222222223</v>
       </c>
       <c r="D349">
-        <v>30.76</v>
+        <v>138.0383333333333</v>
       </c>
     </row>
     <row r="350" spans="1:4">
       <c r="A350" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B350" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C350">
-        <v>13.00944444444444</v>
+        <v>39.34722222222222</v>
       </c>
       <c r="D350">
-        <v>33.3525</v>
+        <v>126.8880555555556</v>
       </c>
     </row>
     <row r="351" spans="1:4">
       <c r="A351" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B351" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="C351">
-        <v>32.64777777777778</v>
+        <v>16.48944444444444</v>
       </c>
       <c r="D351">
-        <v>39.43222222222222</v>
+        <v>79.93972222222222</v>
       </c>
     </row>
     <row r="352" spans="1:4">
       <c r="A352" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B352" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C352">
-        <v>43.29</v>
+        <v>20.13666666666667</v>
       </c>
       <c r="D352">
-        <v>39.13472222222222</v>
+        <v>70.97750000000001</v>
       </c>
     </row>
     <row r="353" spans="1:4">
       <c r="A353" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B353" t="s">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="C353">
-        <v>18.31416666666667</v>
+        <v>18.49861111111111</v>
       </c>
       <c r="D353">
-        <v>36.465</v>
+        <v>77.7475</v>
       </c>
     </row>
     <row r="354" spans="1:4">
       <c r="A354" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B354" t="s">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="C354">
-        <v>17.65277777777778</v>
+        <v>22.11</v>
       </c>
       <c r="D354">
-        <v>37.33111111111111</v>
+        <v>81.71250000000001</v>
       </c>
     </row>
     <row r="355" spans="1:4">
       <c r="A355" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B355" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="C355">
-        <v>17.00361111111111</v>
+        <v>39.34722222222222</v>
       </c>
       <c r="D355">
-        <v>38.26694444444445</v>
+        <v>126.8880555555556</v>
       </c>
     </row>
     <row r="356" spans="1:4">
       <c r="A356" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B356" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="C356">
-        <v>16.57472222222222</v>
+        <v>16.48944444444444</v>
       </c>
       <c r="D356">
-        <v>38.80944444444444</v>
+        <v>79.93972222222222</v>
       </c>
     </row>
     <row r="357" spans="1:4">
       <c r="A357" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B357" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="C357">
-        <v>17.56694444444445</v>
+        <v>20.13666666666667</v>
       </c>
       <c r="D357">
-        <v>39.31777777777778</v>
+        <v>70.97750000000001</v>
       </c>
     </row>
     <row r="358" spans="1:4">
       <c r="A358" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B358" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="C358">
-        <v>19.88861111111111</v>
+        <v>18.49861111111111</v>
       </c>
       <c r="D358">
-        <v>18.66916666666667</v>
+        <v>77.7475</v>
       </c>
     </row>
     <row r="359" spans="1:4">
       <c r="A359" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B359" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="C359">
-        <v>23.93416666666667</v>
+        <v>22.11</v>
       </c>
       <c r="D359">
-        <v>8.970277777777778</v>
+        <v>81.71250000000001</v>
       </c>
     </row>
     <row r="360" spans="1:4">
       <c r="A360" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B360" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C360">
-        <v>19.43472222222222</v>
+        <v>24.61027777777778</v>
       </c>
       <c r="D360">
-        <v>34.5775</v>
+        <v>35.88861111111111</v>
       </c>
     </row>
     <row r="361" spans="1:4">
       <c r="A361" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B361" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C361">
-        <v>17.78583333333333</v>
+        <v>25.49222222222222</v>
       </c>
       <c r="D361">
-        <v>34.6675</v>
+        <v>37.95361111111111</v>
       </c>
     </row>
     <row r="362" spans="1:4">
       <c r="A362" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B362" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C362">
-        <v>7.890833333333333</v>
+        <v>22.89527777777778</v>
       </c>
       <c r="D362">
-        <v>32.53166666666667</v>
+        <v>38.425</v>
       </c>
     </row>
     <row r="363" spans="1:4">
       <c r="A363" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B363" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C363">
-        <v>6.443611111111111</v>
+        <v>28.10138888888889</v>
       </c>
       <c r="D363">
-        <v>28.02888888888889</v>
+        <v>36.18055555555556</v>
       </c>
     </row>
     <row r="364" spans="1:4">
       <c r="A364" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B364" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C364">
-        <v>9.902222222222223</v>
+        <v>32.31555555555556</v>
       </c>
       <c r="D364">
-        <v>27.18833333333333</v>
+        <v>35.67555555555555</v>
       </c>
     </row>
     <row r="365" spans="1:4">
       <c r="A365" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B365" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C365">
-        <v>12.71777777777778</v>
+        <v>34.33666666666667</v>
       </c>
       <c r="D365">
-        <v>27.185</v>
+        <v>38.75027777777778</v>
       </c>
     </row>
     <row r="366" spans="1:4">
       <c r="A366" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B366" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="C366">
-        <v>46.64805555555556</v>
+        <v>38.72222222222222</v>
       </c>
       <c r="D366">
-        <v>97.20166666666667</v>
+        <v>37.31388888888889</v>
       </c>
     </row>
     <row r="367" spans="1:4">
       <c r="A367" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B367" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="C367">
-        <v>46.6725</v>
+        <v>41.90722222222222</v>
       </c>
       <c r="D367">
-        <v>94.59722222222223</v>
+        <v>39.47972222222222</v>
       </c>
     </row>
     <row r="368" spans="1:4">
       <c r="A368" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B368" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="C368">
-        <v>49.28166666666667</v>
+        <v>41.30694444444445</v>
       </c>
       <c r="D368">
-        <v>92.50444444444445</v>
+        <v>37.68944444444445</v>
       </c>
     </row>
     <row r="369" spans="1:4">
       <c r="A369" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B369" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="C369">
-        <v>49.40416666666667</v>
+        <v>13.3525</v>
       </c>
       <c r="D369">
-        <v>94.10916666666667</v>
+        <v>30.76</v>
       </c>
     </row>
     <row r="370" spans="1:4">
       <c r="A370" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B370" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="C370">
-        <v>50.78861111111111</v>
+        <v>13.00944444444444</v>
       </c>
       <c r="D370">
-        <v>104.9333333333333</v>
+        <v>33.3525</v>
       </c>
     </row>
     <row r="371" spans="1:4">
       <c r="A371" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B371" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="C371">
-        <v>56.74194444444444</v>
+        <v>32.64777777777778</v>
       </c>
       <c r="D371">
-        <v>117.3113888888889</v>
+        <v>39.43222222222222</v>
       </c>
     </row>
     <row r="372" spans="1:4">
       <c r="A372" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B372" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="C372">
-        <v>58.08944444444445</v>
+        <v>43.29</v>
       </c>
       <c r="D372">
-        <v>113.5002777777778</v>
+        <v>39.13472222222222</v>
       </c>
     </row>
     <row r="373" spans="1:4">
       <c r="A373" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B373" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C373">
-        <v>61.20111111111111</v>
+        <v>18.31416666666667</v>
       </c>
       <c r="D373">
-        <v>106.0505555555556</v>
+        <v>36.465</v>
       </c>
     </row>
     <row r="374" spans="1:4">
       <c r="A374" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B374" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C374">
-        <v>64.92472222222223</v>
+        <v>17.65277777777778</v>
       </c>
       <c r="D374">
-        <v>92.80416666666666</v>
+        <v>37.33111111111111</v>
       </c>
     </row>
     <row r="375" spans="1:4">
       <c r="A375" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B375" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C375">
-        <v>34.68694444444444</v>
+        <v>17.00361111111111</v>
       </c>
       <c r="D375">
-        <v>111.2963888888889</v>
+        <v>38.26694444444445</v>
       </c>
     </row>
     <row r="376" spans="1:4">
       <c r="A376" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B376" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C376">
-        <v>30.58861111111111</v>
+        <v>16.57472222222222</v>
       </c>
       <c r="D376">
-        <v>117.7855555555556</v>
+        <v>38.80944444444444</v>
       </c>
     </row>
     <row r="377" spans="1:4">
       <c r="A377" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B377" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C377">
-        <v>38.38694444444445</v>
+        <v>17.56694444444445</v>
       </c>
       <c r="D377">
-        <v>129.37</v>
+        <v>39.31777777777778</v>
       </c>
     </row>
     <row r="378" spans="1:4">
       <c r="A378" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B378" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C378">
-        <v>62.20138888888889</v>
+        <v>19.88861111111111</v>
       </c>
       <c r="D378">
-        <v>120.4041666666667</v>
+        <v>18.66916666666667</v>
       </c>
     </row>
     <row r="379" spans="1:4">
       <c r="A379" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B379" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="C379">
-        <v>1.176111111111111</v>
+        <v>23.93416666666667</v>
       </c>
       <c r="D379">
-        <v>0.1908333333333333</v>
+        <v>8.970277777777778</v>
       </c>
     </row>
     <row r="380" spans="1:4">
       <c r="A380" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B380" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="C380">
-        <v>1.212777777777778</v>
+        <v>19.43472222222222</v>
       </c>
       <c r="D380">
-        <v>0.2805555555555556</v>
+        <v>34.5775</v>
       </c>
     </row>
     <row r="381" spans="1:4">
       <c r="A381" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B381" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="C381">
-        <v>1.176111111111111</v>
+        <v>17.78583333333333</v>
       </c>
       <c r="D381">
-        <v>0.2133333333333333</v>
+        <v>34.6675</v>
       </c>
     </row>
     <row r="382" spans="1:4">
       <c r="A382" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B382" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="C382">
-        <v>1.273888888888889</v>
+        <v>7.890833333333333</v>
       </c>
       <c r="D382">
-        <v>0.2580555555555555</v>
+        <v>32.53166666666667</v>
       </c>
     </row>
     <row r="383" spans="1:4">
       <c r="A383" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B383" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="C383">
-        <v>1.273888888888889</v>
+        <v>6.443611111111111</v>
       </c>
       <c r="D383">
-        <v>0.2244444444444444</v>
+        <v>28.02888888888889</v>
       </c>
     </row>
     <row r="384" spans="1:4">
       <c r="A384" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B384" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="C384">
-        <v>1.335277777777778</v>
+        <v>9.902222222222223</v>
       </c>
       <c r="D384">
-        <v>0.2244444444444444</v>
+        <v>27.18833333333333</v>
       </c>
     </row>
     <row r="385" spans="1:4">
       <c r="A385" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B385" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="C385">
-        <v>1.596388888888889</v>
+        <v>12.71777777777778</v>
       </c>
       <c r="D385">
-        <v>0.2244444444444444</v>
+        <v>27.185</v>
       </c>
     </row>
     <row r="386" spans="1:4">
       <c r="A386" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B386" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C386">
-        <v>1.721111111111111</v>
+        <v>46.64805555555556</v>
       </c>
       <c r="D386">
-        <v>0.2355555555555555</v>
+        <v>97.20166666666667</v>
       </c>
     </row>
     <row r="387" spans="1:4">
       <c r="A387" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B387" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C387">
-        <v>1.937777777777778</v>
+        <v>46.6725</v>
       </c>
       <c r="D387">
-        <v>0.2469444444444444</v>
+        <v>94.59722222222223</v>
       </c>
     </row>
     <row r="388" spans="1:4">
       <c r="A388" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B388" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C388">
-        <v>0.9813888888888889</v>
+        <v>49.28166666666667</v>
       </c>
       <c r="D388">
-        <v>0.2469444444444444</v>
+        <v>92.50444444444445</v>
       </c>
     </row>
     <row r="389" spans="1:4">
       <c r="A389" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B389" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C389">
-        <v>1.290277777777778</v>
+        <v>49.40416666666667</v>
       </c>
       <c r="D389">
-        <v>0.2694444444444444</v>
+        <v>94.10916666666667</v>
       </c>
     </row>
     <row r="390" spans="1:4">
       <c r="A390" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B390" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C390">
-        <v>1.577222222222222</v>
+        <v>50.78861111111111</v>
       </c>
       <c r="D390">
-        <v>0.3255555555555555</v>
+        <v>104.9333333333333</v>
       </c>
     </row>
     <row r="391" spans="1:4">
       <c r="A391" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B391" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C391">
-        <v>1.848333333333333</v>
+        <v>56.74194444444444</v>
       </c>
       <c r="D391">
-        <v>0.3816666666666667</v>
+        <v>117.3113888888889</v>
       </c>
     </row>
     <row r="392" spans="1:4">
       <c r="A392" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B392" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="C392">
-        <v>2.866388888888889</v>
+        <v>58.08944444444445</v>
       </c>
       <c r="D392">
-        <v>0.1455555555555555</v>
+        <v>113.5002777777778</v>
       </c>
     </row>
     <row r="393" spans="1:4">
       <c r="A393" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B393" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="C393">
-        <v>3.454444444444444</v>
+        <v>61.20111111111111</v>
       </c>
       <c r="D393">
-        <v>0.1425</v>
+        <v>106.0505555555556</v>
       </c>
     </row>
     <row r="394" spans="1:4">
       <c r="A394" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B394" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="C394">
-        <v>3.466666666666667</v>
+        <v>64.92472222222223</v>
       </c>
       <c r="D394">
-        <v>0.1358333333333333</v>
+        <v>92.80416666666666</v>
       </c>
     </row>
     <row r="395" spans="1:4">
       <c r="A395" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B395" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="C395">
-        <v>3.233888888888889</v>
+        <v>34.68694444444444</v>
       </c>
       <c r="D395">
-        <v>0.1791666666666667</v>
+        <v>111.2963888888889</v>
       </c>
     </row>
     <row r="396" spans="1:4">
       <c r="A396" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B396" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="C396">
-        <v>2.474444444444444</v>
+        <v>30.58861111111111</v>
       </c>
       <c r="D396">
-        <v>0.03583333333333334</v>
+        <v>117.7855555555556</v>
       </c>
     </row>
     <row r="397" spans="1:4">
       <c r="A397" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B397" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="C397">
-        <v>2.633611111111111</v>
+        <v>38.38694444444445</v>
       </c>
       <c r="D397">
-        <v>0.02388888888888889</v>
+        <v>129.37</v>
       </c>
     </row>
     <row r="398" spans="1:4">
       <c r="A398" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B398" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="C398">
-        <v>3.074722222222222</v>
+        <v>62.20138888888889</v>
       </c>
       <c r="D398">
-        <v>0.08361111111111111</v>
+        <v>120.4041666666667</v>
       </c>
     </row>
     <row r="399" spans="1:4">
       <c r="A399" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B399" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C399">
-        <v>3.478888888888889</v>
+        <v>1.176111111111111</v>
       </c>
       <c r="D399">
-        <v>0.12</v>
+        <v>0.1908333333333333</v>
       </c>
     </row>
     <row r="400" spans="1:4">
       <c r="A400" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B400" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C400">
-        <v>3.674722222222222</v>
+        <v>1.212777777777778</v>
       </c>
       <c r="D400">
-        <v>0.1158333333333333</v>
+        <v>0.2805555555555556</v>
       </c>
     </row>
     <row r="401" spans="1:4">
       <c r="A401" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B401" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C401">
-        <v>1.237222222222222</v>
+        <v>1.176111111111111</v>
       </c>
       <c r="D401">
-        <v>0.07972222222222222</v>
+        <v>0.2133333333333333</v>
       </c>
     </row>
     <row r="402" spans="1:4">
       <c r="A402" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B402" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C402">
-        <v>1.564444444444445</v>
+        <v>1.273888888888889</v>
       </c>
       <c r="D402">
-        <v>0.1266666666666667</v>
+        <v>0.2580555555555555</v>
       </c>
     </row>
     <row r="403" spans="1:4">
       <c r="A403" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B403" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C403">
-        <v>2.598333333333333</v>
+        <v>1.273888888888889</v>
       </c>
       <c r="D403">
-        <v>0.0925</v>
+        <v>0.2244444444444444</v>
       </c>
     </row>
     <row r="404" spans="1:4">
       <c r="A404" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B404" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C404">
-        <v>3.003055555555556</v>
+        <v>1.335277777777778</v>
       </c>
       <c r="D404">
-        <v>0.07027777777777777</v>
+        <v>0.2244444444444444</v>
       </c>
     </row>
     <row r="405" spans="1:4">
       <c r="A405" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B405" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="C405">
-        <v>133.2677777777778</v>
+        <v>1.596388888888889</v>
       </c>
       <c r="D405">
-        <v>35.82944444444445</v>
+        <v>0.2244444444444444</v>
       </c>
     </row>
     <row r="406" spans="1:4">
       <c r="A406" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B406" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="C406">
-        <v>129.2008333333333</v>
+        <v>1.721111111111111</v>
       </c>
       <c r="D406">
-        <v>30.69583333333333</v>
+        <v>0.2355555555555555</v>
       </c>
     </row>
     <row r="407" spans="1:4">
       <c r="A407" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B407" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="C407">
-        <v>128.0736111111111</v>
+        <v>1.937777777777778</v>
       </c>
       <c r="D407">
-        <v>31.49083333333333</v>
+        <v>0.2469444444444444</v>
       </c>
     </row>
     <row r="408" spans="1:4">
       <c r="A408" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B408" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="C408">
-        <v>128.0255555555555</v>
+        <v>0.9813888888888889</v>
       </c>
       <c r="D408">
-        <v>31.92555555555555</v>
+        <v>0.2469444444444444</v>
       </c>
     </row>
     <row r="409" spans="1:4">
       <c r="A409" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B409" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="C409">
-        <v>129.2380555555555</v>
+        <v>1.290277777777778</v>
       </c>
       <c r="D409">
-        <v>29.35444444444444</v>
+        <v>0.2694444444444444</v>
       </c>
     </row>
     <row r="410" spans="1:4">
       <c r="A410" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B410" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="C410">
-        <v>129.3238888888889</v>
+        <v>1.577222222222222</v>
       </c>
       <c r="D410">
-        <v>31.11833333333333</v>
+        <v>0.3255555555555555</v>
       </c>
     </row>
     <row r="411" spans="1:4">
       <c r="A411" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B411" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="C411">
-        <v>138.9427777777778</v>
+        <v>1.848333333333333</v>
       </c>
       <c r="D411">
-        <v>26.30277777777778</v>
+        <v>0.3816666666666667</v>
       </c>
     </row>
     <row r="412" spans="1:4">
       <c r="A412" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B412" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C412">
-        <v>139.9469444444445</v>
+        <v>2.866388888888889</v>
       </c>
       <c r="D412">
-        <v>28.64416666666667</v>
+        <v>0.1455555555555555</v>
       </c>
     </row>
     <row r="413" spans="1:4">
       <c r="A413" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B413" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C413">
-        <v>140.3980555555555</v>
+        <v>3.454444444444444</v>
       </c>
       <c r="D413">
-        <v>26.69833333333333</v>
+        <v>0.1425</v>
       </c>
     </row>
     <row r="414" spans="1:4">
       <c r="A414" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B414" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C414">
-        <v>58.20027777777778</v>
+        <v>3.466666666666667</v>
       </c>
       <c r="D414">
-        <v>21.9775</v>
+        <v>0.1358333333333333</v>
       </c>
     </row>
     <row r="415" spans="1:4">
       <c r="A415" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B415" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C415">
-        <v>55.26777777777778</v>
+        <v>3.233888888888889</v>
       </c>
       <c r="D415">
-        <v>22.60972222222222</v>
+        <v>0.1791666666666667</v>
       </c>
     </row>
     <row r="416" spans="1:4">
       <c r="A416" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B416" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C416">
-        <v>109.3866666666667</v>
+        <v>2.474444444444444</v>
       </c>
       <c r="D416">
-        <v>22.87027777777778</v>
+        <v>0.03583333333333334</v>
       </c>
     </row>
     <row r="417" spans="1:4">
       <c r="A417" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B417" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C417">
-        <v>127.6063888888889</v>
+        <v>2.633611111111111</v>
       </c>
       <c r="D417">
-        <v>22.78194444444444</v>
+        <v>0.02388888888888889</v>
       </c>
     </row>
     <row r="418" spans="1:4">
       <c r="A418" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B418" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="C418">
-        <v>251.2230555555556</v>
+        <v>3.074722222222222</v>
       </c>
       <c r="D418">
-        <v>292.6522222222222</v>
+        <v>0.08361111111111111</v>
       </c>
     </row>
     <row r="419" spans="1:4">
       <c r="A419" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B419" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="C419">
-        <v>237.2580555555556</v>
+        <v>3.478888888888889</v>
       </c>
       <c r="D419">
-        <v>208.875</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="420" spans="1:4">
       <c r="A420" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B420" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="C420">
-        <v>242.3786111111111</v>
+        <v>3.674722222222222</v>
       </c>
       <c r="D420">
-        <v>200.8572222222222</v>
+        <v>0.1158333333333333</v>
       </c>
     </row>
     <row r="421" spans="1:4">
       <c r="A421" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B421" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="C421">
-        <v>248.5769444444445</v>
+        <v>1.237222222222222</v>
       </c>
       <c r="D421">
-        <v>199.7672222222222</v>
+        <v>0.07972222222222222</v>
       </c>
     </row>
     <row r="422" spans="1:4">
       <c r="A422" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B422" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="C422">
-        <v>272.5625</v>
+        <v>1.564444444444445</v>
       </c>
       <c r="D422">
-        <v>199.0302777777778</v>
+        <v>0.1266666666666667</v>
       </c>
     </row>
     <row r="423" spans="1:4">
       <c r="A423" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B423" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="C423">
-        <v>283.1463888888889</v>
+        <v>2.598333333333333</v>
       </c>
       <c r="D423">
-        <v>233.0841666666667</v>
+        <v>0.0925</v>
       </c>
     </row>
     <row r="424" spans="1:4">
       <c r="A424" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B424" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="C424">
-        <v>285.1633333333334</v>
+        <v>3.003055555555556</v>
       </c>
       <c r="D424">
-        <v>274.0144444444445</v>
+        <v>0.07027777777777777</v>
       </c>
     </row>
     <row r="425" spans="1:4">
       <c r="A425" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B425" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C425">
-        <v>289.5675</v>
+        <v>133.2677777777778</v>
       </c>
       <c r="D425">
-        <v>237.2283333333333</v>
+        <v>35.82944444444445</v>
       </c>
     </row>
     <row r="426" spans="1:4">
       <c r="A426" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B426" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C426">
-        <v>294.49</v>
+        <v>129.2008333333333</v>
       </c>
       <c r="D426">
-        <v>268.1486111111111</v>
+        <v>30.69583333333333</v>
       </c>
     </row>
     <row r="427" spans="1:4">
       <c r="A427" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B427" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C427">
-        <v>182.2222222222222</v>
+        <v>128.0736111111111</v>
       </c>
       <c r="D427">
-        <v>182.9433333333333</v>
+        <v>31.49083333333333</v>
       </c>
     </row>
     <row r="428" spans="1:4">
       <c r="A428" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B428" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C428">
-        <v>231.5616666666667</v>
+        <v>128.0255555555555</v>
       </c>
       <c r="D428">
-        <v>203.9113888888889</v>
+        <v>31.92555555555555</v>
       </c>
     </row>
     <row r="429" spans="1:4">
       <c r="A429" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B429" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C429">
-        <v>263.5433333333334</v>
+        <v>129.2380555555555</v>
       </c>
       <c r="D429">
-        <v>190.6069444444445</v>
+        <v>29.35444444444444</v>
       </c>
     </row>
     <row r="430" spans="1:4">
       <c r="A430" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B430" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C430">
-        <v>281.2844444444444</v>
+        <v>129.3238888888889</v>
       </c>
       <c r="D430">
-        <v>190.5597222222222</v>
+        <v>31.11833333333333</v>
       </c>
     </row>
     <row r="431" spans="1:4">
       <c r="A431" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B431" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="C431">
-        <v>1.580277777777778</v>
+        <v>138.9427777777778</v>
       </c>
       <c r="D431">
-        <v>3.891944444444444</v>
+        <v>26.30277777777778</v>
       </c>
     </row>
     <row r="432" spans="1:4">
       <c r="A432" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B432" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="C432">
-        <v>0.9186111111111112</v>
+        <v>139.9469444444445</v>
       </c>
       <c r="D432">
-        <v>3.616944444444445</v>
+        <v>28.64416666666667</v>
       </c>
     </row>
     <row r="433" spans="1:4">
       <c r="A433" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B433" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="C433">
-        <v>1.482222222222222</v>
+        <v>140.3980555555555</v>
       </c>
       <c r="D433">
-        <v>3.159444444444444</v>
+        <v>26.69833333333333</v>
       </c>
     </row>
     <row r="434" spans="1:4">
       <c r="A434" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B434" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="C434">
-        <v>2.339722222222222</v>
+        <v>58.20027777777778</v>
       </c>
       <c r="D434">
-        <v>2.93</v>
+        <v>21.9775</v>
       </c>
     </row>
     <row r="435" spans="1:4">
       <c r="A435" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B435" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="C435">
-        <v>5.353333333333333</v>
+        <v>55.26777777777778</v>
       </c>
       <c r="D435">
-        <v>2.746666666666667</v>
+        <v>22.60972222222222</v>
       </c>
     </row>
     <row r="436" spans="1:4">
       <c r="A436" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B436" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="C436">
-        <v>3.895555555555556</v>
+        <v>109.3866666666667</v>
       </c>
       <c r="D436">
-        <v>2.277222222222222</v>
+        <v>22.87027777777778</v>
       </c>
     </row>
     <row r="437" spans="1:4">
       <c r="A437" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B437" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="C437">
-        <v>3.930277777777778</v>
+        <v>127.6063888888889</v>
       </c>
       <c r="D437">
-        <v>1.920277777777778</v>
+        <v>22.78194444444444</v>
       </c>
     </row>
     <row r="438" spans="1:4">
       <c r="A438" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B438" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="C438">
-        <v>3.729166666666667</v>
+        <v>1.937777777777778</v>
       </c>
       <c r="D438">
-        <v>1.543055555555556</v>
+        <v>0.2469444444444444</v>
       </c>
     </row>
     <row r="439" spans="1:4">
       <c r="A439" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B439" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="C439">
-        <v>2.942777777777778</v>
+        <v>0.9813888888888889</v>
       </c>
       <c r="D439">
-        <v>1.116111111111111</v>
+        <v>0.2469444444444444</v>
       </c>
     </row>
     <row r="440" spans="1:4">
       <c r="A440" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B440" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="C440">
-        <v>1.018611111111111</v>
+        <v>1.290277777777778</v>
       </c>
       <c r="D440">
-        <v>0.7813888888888889</v>
+        <v>0.2694444444444444</v>
       </c>
     </row>
     <row r="441" spans="1:4">
       <c r="A441" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B441" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="C441">
-        <v>1.962777777777778</v>
+        <v>1.577222222222222</v>
       </c>
       <c r="D441">
-        <v>0.7891666666666667</v>
+        <v>0.3255555555555555</v>
       </c>
     </row>
     <row r="442" spans="1:4">
       <c r="A442" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B442" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="C442">
-        <v>3.623611111111111</v>
+        <v>1.848333333333333</v>
       </c>
       <c r="D442">
-        <v>0.8522222222222222</v>
+        <v>0.3816666666666667</v>
       </c>
     </row>
     <row r="443" spans="1:4">
       <c r="A443" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B443" t="s">
+        <v>44</v>
+      </c>
+      <c r="C443">
+        <v>251.2230555555556</v>
+      </c>
+      <c r="D443">
+        <v>292.6522222222222</v>
+      </c>
+    </row>
+    <row r="444" spans="1:4">
+      <c r="A444" t="s">
+        <v>41</v>
+      </c>
+      <c r="B444" t="s">
+        <v>45</v>
+      </c>
+      <c r="C444">
+        <v>237.2580555555556</v>
+      </c>
+      <c r="D444">
+        <v>208.875</v>
+      </c>
+    </row>
+    <row r="445" spans="1:4">
+      <c r="A445" t="s">
+        <v>41</v>
+      </c>
+      <c r="B445" t="s">
+        <v>46</v>
+      </c>
+      <c r="C445">
+        <v>242.3786111111111</v>
+      </c>
+      <c r="D445">
+        <v>200.8572222222222</v>
+      </c>
+    </row>
+    <row r="446" spans="1:4">
+      <c r="A446" t="s">
+        <v>41</v>
+      </c>
+      <c r="B446" t="s">
+        <v>47</v>
+      </c>
+      <c r="C446">
+        <v>248.5769444444445</v>
+      </c>
+      <c r="D446">
+        <v>199.7672222222222</v>
+      </c>
+    </row>
+    <row r="447" spans="1:4">
+      <c r="A447" t="s">
+        <v>41</v>
+      </c>
+      <c r="B447" t="s">
+        <v>48</v>
+      </c>
+      <c r="C447">
+        <v>272.5625</v>
+      </c>
+      <c r="D447">
+        <v>199.0302777777778</v>
+      </c>
+    </row>
+    <row r="448" spans="1:4">
+      <c r="A448" t="s">
+        <v>41</v>
+      </c>
+      <c r="B448" t="s">
+        <v>49</v>
+      </c>
+      <c r="C448">
+        <v>283.1463888888889</v>
+      </c>
+      <c r="D448">
+        <v>233.0841666666667</v>
+      </c>
+    </row>
+    <row r="449" spans="1:4">
+      <c r="A449" t="s">
+        <v>41</v>
+      </c>
+      <c r="B449" t="s">
         <v>50</v>
       </c>
-      <c r="C443">
+      <c r="C449">
+        <v>285.1633333333334</v>
+      </c>
+      <c r="D449">
+        <v>274.0144444444445</v>
+      </c>
+    </row>
+    <row r="450" spans="1:4">
+      <c r="A450" t="s">
+        <v>41</v>
+      </c>
+      <c r="B450" t="s">
+        <v>51</v>
+      </c>
+      <c r="C450">
+        <v>289.5675</v>
+      </c>
+      <c r="D450">
+        <v>237.2283333333333</v>
+      </c>
+    </row>
+    <row r="451" spans="1:4">
+      <c r="A451" t="s">
+        <v>41</v>
+      </c>
+      <c r="B451" t="s">
+        <v>52</v>
+      </c>
+      <c r="C451">
+        <v>294.49</v>
+      </c>
+      <c r="D451">
+        <v>268.1486111111111</v>
+      </c>
+    </row>
+    <row r="452" spans="1:4">
+      <c r="A452" t="s">
+        <v>41</v>
+      </c>
+      <c r="B452" t="s">
+        <v>53</v>
+      </c>
+      <c r="C452">
+        <v>182.2222222222222</v>
+      </c>
+      <c r="D452">
+        <v>182.9433333333333</v>
+      </c>
+    </row>
+    <row r="453" spans="1:4">
+      <c r="A453" t="s">
+        <v>41</v>
+      </c>
+      <c r="B453" t="s">
+        <v>54</v>
+      </c>
+      <c r="C453">
+        <v>231.5616666666667</v>
+      </c>
+      <c r="D453">
+        <v>203.9113888888889</v>
+      </c>
+    </row>
+    <row r="454" spans="1:4">
+      <c r="A454" t="s">
+        <v>41</v>
+      </c>
+      <c r="B454" t="s">
+        <v>55</v>
+      </c>
+      <c r="C454">
+        <v>263.5433333333334</v>
+      </c>
+      <c r="D454">
+        <v>190.6069444444445</v>
+      </c>
+    </row>
+    <row r="455" spans="1:4">
+      <c r="A455" t="s">
+        <v>41</v>
+      </c>
+      <c r="B455" t="s">
+        <v>56</v>
+      </c>
+      <c r="C455">
+        <v>281.2844444444444</v>
+      </c>
+      <c r="D455">
+        <v>190.5597222222222</v>
+      </c>
+    </row>
+    <row r="456" spans="1:4">
+      <c r="A456" t="s">
+        <v>42</v>
+      </c>
+      <c r="B456" t="s">
+        <v>44</v>
+      </c>
+      <c r="C456">
+        <v>1.580277777777778</v>
+      </c>
+      <c r="D456">
+        <v>3.891944444444444</v>
+      </c>
+    </row>
+    <row r="457" spans="1:4">
+      <c r="A457" t="s">
+        <v>42</v>
+      </c>
+      <c r="B457" t="s">
+        <v>45</v>
+      </c>
+      <c r="C457">
+        <v>0.9186111111111112</v>
+      </c>
+      <c r="D457">
+        <v>3.616944444444445</v>
+      </c>
+    </row>
+    <row r="458" spans="1:4">
+      <c r="A458" t="s">
+        <v>42</v>
+      </c>
+      <c r="B458" t="s">
+        <v>46</v>
+      </c>
+      <c r="C458">
+        <v>1.482222222222222</v>
+      </c>
+      <c r="D458">
+        <v>3.159444444444444</v>
+      </c>
+    </row>
+    <row r="459" spans="1:4">
+      <c r="A459" t="s">
+        <v>42</v>
+      </c>
+      <c r="B459" t="s">
+        <v>47</v>
+      </c>
+      <c r="C459">
+        <v>2.339722222222222</v>
+      </c>
+      <c r="D459">
+        <v>2.93</v>
+      </c>
+    </row>
+    <row r="460" spans="1:4">
+      <c r="A460" t="s">
+        <v>42</v>
+      </c>
+      <c r="B460" t="s">
+        <v>48</v>
+      </c>
+      <c r="C460">
+        <v>5.353333333333333</v>
+      </c>
+      <c r="D460">
+        <v>2.746666666666667</v>
+      </c>
+    </row>
+    <row r="461" spans="1:4">
+      <c r="A461" t="s">
+        <v>42</v>
+      </c>
+      <c r="B461" t="s">
+        <v>49</v>
+      </c>
+      <c r="C461">
+        <v>3.895555555555556</v>
+      </c>
+      <c r="D461">
+        <v>2.277222222222222</v>
+      </c>
+    </row>
+    <row r="462" spans="1:4">
+      <c r="A462" t="s">
+        <v>42</v>
+      </c>
+      <c r="B462" t="s">
+        <v>50</v>
+      </c>
+      <c r="C462">
+        <v>3.930277777777778</v>
+      </c>
+      <c r="D462">
+        <v>1.920277777777778</v>
+      </c>
+    </row>
+    <row r="463" spans="1:4">
+      <c r="A463" t="s">
+        <v>42</v>
+      </c>
+      <c r="B463" t="s">
+        <v>51</v>
+      </c>
+      <c r="C463">
+        <v>3.729166666666667</v>
+      </c>
+      <c r="D463">
+        <v>1.543055555555556</v>
+      </c>
+    </row>
+    <row r="464" spans="1:4">
+      <c r="A464" t="s">
+        <v>42</v>
+      </c>
+      <c r="B464" t="s">
+        <v>52</v>
+      </c>
+      <c r="C464">
+        <v>2.942777777777778</v>
+      </c>
+      <c r="D464">
+        <v>1.116111111111111</v>
+      </c>
+    </row>
+    <row r="465" spans="1:4">
+      <c r="A465" t="s">
+        <v>42</v>
+      </c>
+      <c r="B465" t="s">
+        <v>53</v>
+      </c>
+      <c r="C465">
+        <v>1.018611111111111</v>
+      </c>
+      <c r="D465">
+        <v>0.7813888888888889</v>
+      </c>
+    </row>
+    <row r="466" spans="1:4">
+      <c r="A466" t="s">
+        <v>42</v>
+      </c>
+      <c r="B466" t="s">
+        <v>54</v>
+      </c>
+      <c r="C466">
+        <v>1.962777777777778</v>
+      </c>
+      <c r="D466">
+        <v>0.7891666666666667</v>
+      </c>
+    </row>
+    <row r="467" spans="1:4">
+      <c r="A467" t="s">
+        <v>42</v>
+      </c>
+      <c r="B467" t="s">
+        <v>55</v>
+      </c>
+      <c r="C467">
+        <v>3.623611111111111</v>
+      </c>
+      <c r="D467">
+        <v>0.8522222222222222</v>
+      </c>
+    </row>
+    <row r="468" spans="1:4">
+      <c r="A468" t="s">
+        <v>42</v>
+      </c>
+      <c r="B468" t="s">
+        <v>56</v>
+      </c>
+      <c r="C468">
         <v>5.216666666666667</v>
       </c>
-      <c r="D443">
+      <c r="D468">
+        <v>0.8863888888888889</v>
+      </c>
+    </row>
+    <row r="469" spans="1:4">
+      <c r="A469" t="s">
+        <v>43</v>
+      </c>
+      <c r="B469" t="s">
+        <v>52</v>
+      </c>
+      <c r="C469">
+        <v>2.942777777777778</v>
+      </c>
+      <c r="D469">
+        <v>1.116111111111111</v>
+      </c>
+    </row>
+    <row r="470" spans="1:4">
+      <c r="A470" t="s">
+        <v>43</v>
+      </c>
+      <c r="B470" t="s">
+        <v>53</v>
+      </c>
+      <c r="C470">
+        <v>1.018611111111111</v>
+      </c>
+      <c r="D470">
+        <v>0.7813888888888889</v>
+      </c>
+    </row>
+    <row r="471" spans="1:4">
+      <c r="A471" t="s">
+        <v>43</v>
+      </c>
+      <c r="B471" t="s">
+        <v>54</v>
+      </c>
+      <c r="C471">
+        <v>1.962777777777778</v>
+      </c>
+      <c r="D471">
+        <v>0.7891666666666667</v>
+      </c>
+    </row>
+    <row r="472" spans="1:4">
+      <c r="A472" t="s">
+        <v>43</v>
+      </c>
+      <c r="B472" t="s">
+        <v>55</v>
+      </c>
+      <c r="C472">
+        <v>3.623611111111111</v>
+      </c>
+      <c r="D472">
+        <v>0.8522222222222222</v>
+      </c>
+    </row>
+    <row r="473" spans="1:4">
+      <c r="A473" t="s">
+        <v>43</v>
+      </c>
+      <c r="B473" t="s">
+        <v>56</v>
+      </c>
+      <c r="C473">
+        <v>5.216666666666667</v>
+      </c>
+      <c r="D473">
         <v>0.8863888888888889</v>
       </c>
     </row>
